--- a/assets/guncel_deneme_bonuslari_listesi.xlsx
+++ b/assets/guncel_deneme_bonuslari_listesi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cengi\Desktop\test\Deneme Bonusu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015050E5-3AAE-4545-99FC-4A8217B556C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF05BD0-3A3B-4E76-9D50-C85865590EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD7B2693-F8D1-429F-9AB3-DB64ACA5183F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD7B2693-F8D1-429F-9AB3-DB64ACA5183F}"/>
   </bookViews>
   <sheets>
     <sheet name="guncel_deneme_bonuslari_listesi" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="641">
   <si>
     <t>maks 750tl çekim</t>
   </si>
@@ -1940,6 +1940,12 @@
   </si>
   <si>
     <t>zibilyonbet</t>
+  </si>
+  <si>
+    <t>casinoforbet</t>
+  </si>
+  <si>
+    <t>hellocasino</t>
   </si>
 </sst>
 </file>
@@ -2441,9 +2447,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="%20 - Vurgu1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2830,7 +2835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F56ED3D-A3F2-450D-9EAE-1214C3EA2069}">
-  <dimension ref="A1:D484"/>
+  <dimension ref="A1:D486"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -4650,21 +4655,24 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>542</v>
+        <v>639</v>
       </c>
       <c r="B156" t="s">
-        <v>543</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D156" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>145</v>
+        <v>542</v>
       </c>
       <c r="B157" t="s">
-        <v>146</v>
+        <v>543</v>
       </c>
       <c r="C157" t="s">
         <v>2</v>
@@ -4672,24 +4680,21 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>544</v>
+        <v>145</v>
       </c>
       <c r="B158" t="s">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="C158" t="s">
-        <v>1</v>
-      </c>
-      <c r="D158" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
       <c r="B159" t="s">
-        <v>545</v>
+        <v>9</v>
       </c>
       <c r="C159" t="s">
         <v>1</v>
@@ -4700,13 +4705,13 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>546</v>
+        <v>417</v>
       </c>
       <c r="B160" t="s">
-        <v>38</v>
+        <v>545</v>
       </c>
       <c r="C160" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D160" t="s">
         <v>415</v>
@@ -4714,10 +4719,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>147</v>
+        <v>546</v>
       </c>
       <c r="B161" t="s">
-        <v>453</v>
+        <v>38</v>
       </c>
       <c r="C161" t="s">
         <v>2</v>
@@ -4728,29 +4733,32 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B162" t="s">
-        <v>9</v>
+        <v>453</v>
       </c>
       <c r="C162" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D162" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>148</v>
+      </c>
+      <c r="B163" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>149</v>
-      </c>
-      <c r="B163" t="s">
-        <v>9</v>
-      </c>
-      <c r="C163" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="B164" t="s">
         <v>9</v>
@@ -4761,24 +4769,21 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>9</v>
       </c>
       <c r="C165" t="s">
         <v>1</v>
-      </c>
-      <c r="D165" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B166" t="s">
-        <v>547</v>
+        <v>257</v>
       </c>
       <c r="C166" t="s">
         <v>1</v>
@@ -4789,21 +4794,24 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>150</v>
+        <v>418</v>
       </c>
       <c r="B167" t="s">
-        <v>13</v>
+        <v>547</v>
       </c>
       <c r="C167" t="s">
         <v>1</v>
+      </c>
+      <c r="D167" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>455</v>
+        <v>150</v>
       </c>
       <c r="B168" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
         <v>1</v>
@@ -4811,46 +4819,46 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>151</v>
+        <v>455</v>
       </c>
       <c r="B169" t="s">
-        <v>548</v>
+        <v>9</v>
       </c>
       <c r="C169" t="s">
-        <v>2</v>
-      </c>
-      <c r="D169" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B170" t="s">
-        <v>68</v>
+        <v>548</v>
       </c>
       <c r="C170" t="s">
         <v>2</v>
+      </c>
+      <c r="D170" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B171" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C171" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B172" t="s">
-        <v>549</v>
+        <v>13</v>
       </c>
       <c r="C172" t="s">
         <v>1</v>
@@ -4858,46 +4866,46 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B173" t="s">
-        <v>20</v>
+        <v>549</v>
       </c>
       <c r="C173" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>421</v>
+        <v>155</v>
       </c>
       <c r="B174" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C174" t="s">
-        <v>1</v>
-      </c>
-      <c r="D174" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>156</v>
+        <v>421</v>
       </c>
       <c r="B175" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C175" t="s">
         <v>1</v>
+      </c>
+      <c r="D175" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B176" t="s">
-        <v>456</v>
+        <v>9</v>
       </c>
       <c r="C176" t="s">
         <v>1</v>
@@ -4905,35 +4913,35 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>457</v>
+        <v>157</v>
       </c>
       <c r="B177" t="s">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="C177" t="s">
-        <v>2</v>
-      </c>
-      <c r="D177" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>158</v>
+        <v>457</v>
       </c>
       <c r="B178" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C178" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D178" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B179" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C179" t="s">
         <v>1</v>
@@ -4941,10 +4949,10 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B180" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="C180" t="s">
         <v>1</v>
@@ -4952,71 +4960,71 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B181" t="s">
-        <v>550</v>
+        <v>91</v>
       </c>
       <c r="C181" t="s">
-        <v>2</v>
-      </c>
-      <c r="D181" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B182" t="s">
-        <v>13</v>
+        <v>550</v>
       </c>
       <c r="C182" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D182" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>636</v>
+        <v>162</v>
       </c>
       <c r="B183" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C183" t="s">
         <v>1</v>
-      </c>
-      <c r="D183" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>163</v>
+        <v>636</v>
       </c>
       <c r="B184" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C184" t="s">
         <v>1</v>
+      </c>
+      <c r="D184" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>458</v>
+        <v>163</v>
       </c>
       <c r="B185" t="s">
-        <v>459</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>582</v>
+        <v>458</v>
       </c>
       <c r="B186" t="s">
-        <v>583</v>
+        <v>459</v>
       </c>
       <c r="C186" t="s">
         <v>2</v>
@@ -5024,10 +5032,10 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>164</v>
+        <v>582</v>
       </c>
       <c r="B187" t="s">
-        <v>165</v>
+        <v>583</v>
       </c>
       <c r="C187" t="s">
         <v>2</v>
@@ -5035,10 +5043,10 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B188" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="C188" t="s">
         <v>2</v>
@@ -5046,57 +5054,57 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>460</v>
+        <v>166</v>
       </c>
       <c r="B189" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C189" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B190" t="s">
-        <v>462</v>
+        <v>11</v>
       </c>
       <c r="C190" t="s">
-        <v>2</v>
-      </c>
-      <c r="D190" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>167</v>
+        <v>461</v>
       </c>
       <c r="B191" t="s">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="C191" t="s">
         <v>2</v>
+      </c>
+      <c r="D191" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B192" t="s">
-        <v>9</v>
+        <v>551</v>
       </c>
       <c r="C192" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B193" t="s">
-        <v>552</v>
+        <v>9</v>
       </c>
       <c r="C193" t="s">
         <v>1</v>
@@ -5104,10 +5112,10 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B194" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C194" t="s">
         <v>1</v>
@@ -5115,68 +5123,68 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B195" t="s">
-        <v>172</v>
+        <v>553</v>
       </c>
       <c r="C195" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B196" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="C196" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>554</v>
+        <v>173</v>
       </c>
       <c r="B197" t="s">
         <v>9</v>
       </c>
       <c r="C197" t="s">
         <v>1</v>
-      </c>
-      <c r="D197" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>174</v>
+        <v>554</v>
       </c>
       <c r="B198" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C198" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D198" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B199" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C199" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B200" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C200" t="s">
         <v>1</v>
@@ -5184,79 +5192,79 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>555</v>
+        <v>176</v>
       </c>
       <c r="B201" t="s">
-        <v>556</v>
+        <v>9</v>
       </c>
       <c r="C201" t="s">
         <v>1</v>
-      </c>
-      <c r="D201" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>463</v>
+        <v>555</v>
       </c>
       <c r="B202" t="s">
-        <v>479</v>
+        <v>556</v>
       </c>
       <c r="C202" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D202" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>177</v>
+        <v>463</v>
       </c>
       <c r="B203" t="s">
-        <v>558</v>
+        <v>479</v>
       </c>
       <c r="C203" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>559</v>
+        <v>177</v>
       </c>
       <c r="B204" t="s">
-        <v>9</v>
+        <v>558</v>
       </c>
       <c r="C204" t="s">
         <v>1</v>
-      </c>
-      <c r="D204" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>178</v>
+        <v>559</v>
       </c>
       <c r="B205" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C205" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D205" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B206" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C206" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B207" t="s">
         <v>13</v>
@@ -5267,7 +5275,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>424</v>
+        <v>180</v>
       </c>
       <c r="B208" t="s">
         <v>13</v>
@@ -5275,107 +5283,107 @@
       <c r="C208" t="s">
         <v>1</v>
       </c>
-      <c r="D208" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>181</v>
+        <v>424</v>
       </c>
       <c r="B209" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C209" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D209" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B210" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C210" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B211" t="s">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="C211" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="B212" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="C212" t="s">
-        <v>1</v>
-      </c>
-      <c r="D212" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>464</v>
+        <v>560</v>
       </c>
       <c r="B213" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C213" t="s">
         <v>1</v>
+      </c>
+      <c r="D213" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B214" t="s">
-        <v>466</v>
+        <v>9</v>
       </c>
       <c r="C214" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>185</v>
+        <v>465</v>
       </c>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>466</v>
       </c>
       <c r="C215" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B216" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="C216" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>467</v>
+        <v>186</v>
       </c>
       <c r="B217" t="s">
-        <v>548</v>
+        <v>187</v>
       </c>
       <c r="C217" t="s">
         <v>2</v>
@@ -5383,10 +5391,10 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>188</v>
+        <v>467</v>
       </c>
       <c r="B218" t="s">
-        <v>38</v>
+        <v>548</v>
       </c>
       <c r="C218" t="s">
         <v>2</v>
@@ -5394,21 +5402,21 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B219" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C219" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B220" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C220" t="s">
         <v>1</v>
@@ -5416,21 +5424,18 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>561</v>
+        <v>190</v>
       </c>
       <c r="B221" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C221" t="s">
-        <v>2</v>
-      </c>
-      <c r="D221" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B222" t="s">
         <v>38</v>
@@ -5444,13 +5449,13 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B223" t="s">
-        <v>564</v>
+        <v>38</v>
       </c>
       <c r="C223" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D223" t="s">
         <v>415</v>
@@ -5458,21 +5463,24 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>191</v>
+        <v>563</v>
       </c>
       <c r="B224" t="s">
-        <v>20</v>
+        <v>564</v>
       </c>
       <c r="C224" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D224" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B225" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="C225" t="s">
         <v>2</v>
@@ -5480,21 +5488,21 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B226" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="C226" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B227" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C227" t="s">
         <v>1</v>
@@ -5502,46 +5510,46 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>423</v>
+        <v>194</v>
       </c>
       <c r="B228" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="C228" t="s">
-        <v>2</v>
-      </c>
-      <c r="D228" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>195</v>
+        <v>423</v>
       </c>
       <c r="B229" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="C229" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D229" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B230" t="s">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="C230" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B231" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="C231" t="s">
         <v>2</v>
@@ -5549,74 +5557,71 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B232" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C232" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B233" t="s">
-        <v>468</v>
+        <v>9</v>
       </c>
       <c r="C233" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>566</v>
+        <v>200</v>
       </c>
       <c r="B234" t="s">
-        <v>136</v>
+        <v>468</v>
       </c>
       <c r="C234" t="s">
-        <v>1</v>
-      </c>
-      <c r="D234" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>201</v>
+        <v>566</v>
       </c>
       <c r="B235" t="s">
-        <v>257</v>
+        <v>136</v>
       </c>
       <c r="C235" t="s">
         <v>1</v>
+      </c>
+      <c r="D235" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>567</v>
+        <v>201</v>
       </c>
       <c r="B236" t="s">
-        <v>568</v>
+        <v>257</v>
       </c>
       <c r="C236" t="s">
-        <v>2</v>
-      </c>
-      <c r="D236" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B237" t="s">
-        <v>9</v>
+        <v>568</v>
       </c>
       <c r="C237" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237" t="s">
         <v>415</v>
@@ -5624,54 +5629,60 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>202</v>
+        <v>569</v>
       </c>
       <c r="B238" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="C238" t="s">
         <v>1</v>
+      </c>
+      <c r="D238" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B239" t="s">
-        <v>254</v>
+        <v>93</v>
       </c>
       <c r="C239" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>469</v>
+        <v>203</v>
       </c>
       <c r="B240" t="s">
-        <v>13</v>
+        <v>254</v>
       </c>
       <c r="C240" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>204</v>
+        <v>640</v>
       </c>
       <c r="B241" t="s">
-        <v>570</v>
+        <v>11</v>
       </c>
       <c r="C241" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D241" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>205</v>
+        <v>469</v>
       </c>
       <c r="B242" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C242" t="s">
         <v>1</v>
@@ -5679,32 +5690,32 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B243" t="s">
-        <v>13</v>
+        <v>570</v>
       </c>
       <c r="C243" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B244" t="s">
-        <v>571</v>
+        <v>9</v>
       </c>
       <c r="C244" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B245" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C245" t="s">
         <v>1</v>
@@ -5712,10 +5723,10 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B246" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="C246" t="s">
         <v>2</v>
@@ -5723,10 +5734,10 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B247" t="s">
-        <v>211</v>
+        <v>9</v>
       </c>
       <c r="C247" t="s">
         <v>1</v>
@@ -5734,32 +5745,32 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B248" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="C248" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B249" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C249" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B250" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C250" t="s">
         <v>1</v>
@@ -5767,10 +5778,10 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B251" t="s">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="C251" t="s">
         <v>2</v>
@@ -5778,21 +5789,18 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>574</v>
+        <v>215</v>
       </c>
       <c r="B252" t="s">
-        <v>38</v>
+        <v>573</v>
       </c>
       <c r="C252" t="s">
-        <v>2</v>
-      </c>
-      <c r="D252" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B253" t="s">
         <v>20</v>
@@ -5800,19 +5808,16 @@
       <c r="C253" t="s">
         <v>2</v>
       </c>
-      <c r="D253" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>218</v>
+        <v>574</v>
       </c>
       <c r="B254" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C254" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D254" t="s">
         <v>415</v>
@@ -5820,29 +5825,35 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B255" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C255" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D255" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B256" t="s">
-        <v>221</v>
+        <v>9</v>
       </c>
       <c r="C256" t="s">
         <v>1</v>
+      </c>
+      <c r="D256" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B257" t="s">
         <v>9</v>
@@ -5853,10 +5864,10 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B258" t="s">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="C258" t="s">
         <v>1</v>
@@ -5864,46 +5875,46 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>575</v>
+        <v>222</v>
       </c>
       <c r="B259" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C259" t="s">
-        <v>2</v>
-      </c>
-      <c r="D259" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>470</v>
+        <v>223</v>
       </c>
       <c r="B260" t="s">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="C260" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>224</v>
+        <v>575</v>
       </c>
       <c r="B261" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C261" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D261" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>225</v>
+        <v>470</v>
       </c>
       <c r="B262" t="s">
-        <v>576</v>
+        <v>197</v>
       </c>
       <c r="C262" t="s">
         <v>2</v>
@@ -5911,43 +5922,40 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B263" t="s">
-        <v>214</v>
+        <v>9</v>
       </c>
       <c r="C263" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B264" t="s">
-        <v>13</v>
+        <v>576</v>
       </c>
       <c r="C264" t="s">
-        <v>1</v>
-      </c>
-      <c r="D264" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>422</v>
+        <v>226</v>
       </c>
       <c r="B265" t="s">
-        <v>9</v>
+        <v>214</v>
       </c>
       <c r="C265" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B266" t="s">
         <v>13</v>
@@ -5955,85 +5963,85 @@
       <c r="C266" t="s">
         <v>1</v>
       </c>
+      <c r="D266" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>577</v>
+        <v>422</v>
       </c>
       <c r="B267" t="s">
         <v>9</v>
       </c>
       <c r="C267" t="s">
         <v>1</v>
-      </c>
-      <c r="D267" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B268" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C268" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>471</v>
+        <v>577</v>
       </c>
       <c r="B269" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C269" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D269" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B270" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C270" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>231</v>
+        <v>471</v>
       </c>
       <c r="B271" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C271" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>578</v>
+        <v>230</v>
       </c>
       <c r="B272" t="s">
-        <v>579</v>
+        <v>9</v>
       </c>
       <c r="C272" t="s">
         <v>1</v>
-      </c>
-      <c r="D272" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>472</v>
+        <v>231</v>
       </c>
       <c r="B273" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C273" t="s">
         <v>1</v>
@@ -6041,21 +6049,24 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>232</v>
+        <v>578</v>
       </c>
       <c r="B274" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C274" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D274" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>233</v>
+        <v>472</v>
       </c>
       <c r="B275" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C275" t="s">
         <v>1</v>
@@ -6063,21 +6074,21 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B276" t="s">
-        <v>9</v>
+        <v>580</v>
       </c>
       <c r="C276" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A277" s="1" t="s">
-        <v>235</v>
+      <c r="A277" t="s">
+        <v>233</v>
       </c>
       <c r="B277" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="C277" t="s">
         <v>1</v>
@@ -6085,49 +6096,46 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B278" t="s">
         <v>9</v>
       </c>
       <c r="C278" t="s">
         <v>1</v>
-      </c>
-      <c r="D278" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>584</v>
+        <v>235</v>
       </c>
       <c r="B279" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="C279" t="s">
         <v>1</v>
-      </c>
-      <c r="D279" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B280" t="s">
-        <v>238</v>
+        <v>9</v>
       </c>
       <c r="C280" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D280" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B281" t="s">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="C281" t="s">
         <v>1</v>
@@ -6138,10 +6146,10 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B282" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C282" t="s">
         <v>2</v>
@@ -6149,10 +6157,10 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B283" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C283" t="s">
         <v>1</v>
@@ -6163,32 +6171,35 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B284" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C284" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>243</v>
+        <v>586</v>
       </c>
       <c r="B285" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="C285" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D285" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B286" t="s">
-        <v>13</v>
+        <v>242</v>
       </c>
       <c r="C286" t="s">
         <v>1</v>
@@ -6196,57 +6207,54 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B287" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="C287" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B288" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="C288" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B289" t="s">
-        <v>197</v>
+        <v>30</v>
       </c>
       <c r="C289" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>428</v>
+        <v>246</v>
       </c>
       <c r="B290" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="C290" t="s">
-        <v>1</v>
-      </c>
-      <c r="D290" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B291" t="s">
-        <v>38</v>
+        <v>197</v>
       </c>
       <c r="C291" t="s">
         <v>2</v>
@@ -6254,21 +6262,24 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>249</v>
+        <v>428</v>
       </c>
       <c r="B292" t="s">
-        <v>250</v>
+        <v>9</v>
       </c>
       <c r="C292" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D292" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B293" t="s">
-        <v>252</v>
+        <v>38</v>
       </c>
       <c r="C293" t="s">
         <v>2</v>
@@ -6276,10 +6287,10 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B294" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C294" t="s">
         <v>2</v>
@@ -6287,71 +6298,68 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>587</v>
+        <v>251</v>
       </c>
       <c r="B295" t="s">
-        <v>9</v>
+        <v>252</v>
       </c>
       <c r="C295" t="s">
-        <v>1</v>
-      </c>
-      <c r="D295" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>425</v>
+        <v>253</v>
       </c>
       <c r="B296" t="s">
-        <v>9</v>
+        <v>254</v>
       </c>
       <c r="C296" t="s">
-        <v>1</v>
-      </c>
-      <c r="D296" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>255</v>
+        <v>587</v>
       </c>
       <c r="B297" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C297" t="s">
         <v>1</v>
+      </c>
+      <c r="D297" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>256</v>
+        <v>425</v>
       </c>
       <c r="B298" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C298" t="s">
         <v>1</v>
+      </c>
+      <c r="D298" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>588</v>
+        <v>255</v>
       </c>
       <c r="B299" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C299" t="s">
-        <v>2</v>
-      </c>
-      <c r="D299" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B300" t="s">
         <v>13</v>
@@ -6362,54 +6370,57 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>259</v>
+        <v>588</v>
       </c>
       <c r="B301" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C301" t="s">
         <v>2</v>
+      </c>
+      <c r="D301" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>589</v>
+        <v>258</v>
       </c>
       <c r="B302" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C302" t="s">
         <v>1</v>
-      </c>
-      <c r="D302" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B303" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C303" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>261</v>
+        <v>589</v>
       </c>
       <c r="B304" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C304" t="s">
         <v>1</v>
+      </c>
+      <c r="D304" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B305" t="s">
         <v>9</v>
@@ -6420,10 +6431,10 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B306" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="C306" t="s">
         <v>1</v>
@@ -6431,21 +6442,21 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B307" t="s">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="C307" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B308" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C308" t="s">
         <v>1</v>
@@ -6453,68 +6464,65 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B309" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="C309" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B310" t="s">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="C310" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B311" t="s">
-        <v>270</v>
+        <v>9</v>
       </c>
       <c r="C311" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B312" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C312" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>590</v>
+        <v>269</v>
       </c>
       <c r="B313" t="s">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="C313" t="s">
-        <v>1</v>
-      </c>
-      <c r="D313" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B314" t="s">
-        <v>9</v>
+        <v>272</v>
       </c>
       <c r="C314" t="s">
         <v>1</v>
@@ -6522,32 +6530,35 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>275</v>
+        <v>590</v>
       </c>
       <c r="B315" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="C315" t="s">
         <v>1</v>
+      </c>
+      <c r="D315" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>473</v>
+        <v>274</v>
       </c>
       <c r="B316" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="C316" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B317" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="C317" t="s">
         <v>1</v>
@@ -6555,24 +6566,21 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
       <c r="B318" t="s">
-        <v>592</v>
+        <v>77</v>
       </c>
       <c r="C318" t="s">
         <v>2</v>
-      </c>
-      <c r="D318" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B319" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C319" t="s">
         <v>1</v>
@@ -6580,10 +6588,10 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B320" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C320" t="s">
         <v>2</v>
@@ -6594,7 +6602,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B321" t="s">
         <v>9</v>
@@ -6605,21 +6613,24 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>279</v>
+        <v>593</v>
       </c>
       <c r="B322" t="s">
-        <v>9</v>
+        <v>594</v>
       </c>
       <c r="C322" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D322" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B323" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C323" t="s">
         <v>1</v>
@@ -6627,7 +6638,7 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B324" t="s">
         <v>9</v>
@@ -6638,10 +6649,10 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B325" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C325" t="s">
         <v>1</v>
@@ -6649,32 +6660,32 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>474</v>
+        <v>281</v>
       </c>
       <c r="B326" t="s">
-        <v>452</v>
+        <v>9</v>
       </c>
       <c r="C326" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>475</v>
+        <v>282</v>
       </c>
       <c r="B327" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C327" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>283</v>
+        <v>474</v>
       </c>
       <c r="B328" t="s">
-        <v>273</v>
+        <v>452</v>
       </c>
       <c r="C328" t="s">
         <v>2</v>
@@ -6682,71 +6693,68 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>284</v>
+        <v>475</v>
       </c>
       <c r="B329" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C329" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B330" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="C330" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B331" t="s">
-        <v>287</v>
+        <v>9</v>
       </c>
       <c r="C331" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>285</v>
+      </c>
+      <c r="B332" t="s">
+        <v>9</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>286</v>
+      </c>
+      <c r="B333" t="s">
+        <v>287</v>
+      </c>
+      <c r="C333" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
         <v>595</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B334" t="s">
         <v>596</v>
       </c>
-      <c r="C332" t="s">
-        <v>1</v>
-      </c>
-      <c r="D332" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A333" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B333" t="s">
-        <v>13</v>
-      </c>
-      <c r="C333" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="B334" t="s">
-        <v>293</v>
-      </c>
       <c r="C334" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D334" t="s">
         <v>415</v>
@@ -6754,32 +6762,35 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="B335" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C335" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>289</v>
+        <v>597</v>
       </c>
       <c r="B336" t="s">
-        <v>13</v>
+        <v>293</v>
       </c>
       <c r="C336" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D336" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B337" t="s">
-        <v>466</v>
+        <v>68</v>
       </c>
       <c r="C337" t="s">
         <v>2</v>
@@ -6787,10 +6798,10 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B338" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C338" t="s">
         <v>1</v>
@@ -6798,10 +6809,10 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B339" t="s">
-        <v>20</v>
+        <v>466</v>
       </c>
       <c r="C339" t="s">
         <v>2</v>
@@ -6809,43 +6820,43 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B340" t="s">
-        <v>477</v>
+        <v>9</v>
       </c>
       <c r="C340" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B341" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="C341" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B342" t="s">
-        <v>136</v>
+        <v>477</v>
       </c>
       <c r="C342" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B343" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="C343" t="s">
         <v>1</v>
@@ -6853,21 +6864,21 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B344" t="s">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="C344" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B345" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="C345" t="s">
         <v>1</v>
@@ -6875,68 +6886,68 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>497</v>
+        <v>298</v>
       </c>
       <c r="B346" t="s">
-        <v>9</v>
+        <v>240</v>
       </c>
       <c r="C346" t="s">
-        <v>1</v>
-      </c>
-      <c r="D346" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B347" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="C347" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>301</v>
+        <v>497</v>
       </c>
       <c r="B348" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C348" t="s">
         <v>1</v>
+      </c>
+      <c r="D348" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>478</v>
+        <v>300</v>
       </c>
       <c r="B349" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C349" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B350" t="s">
-        <v>293</v>
+        <v>11</v>
       </c>
       <c r="C350" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>303</v>
+        <v>478</v>
       </c>
       <c r="B351" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C351" t="s">
         <v>1</v>
@@ -6944,10 +6955,10 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B352" t="s">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="C352" t="s">
         <v>2</v>
@@ -6955,7 +6966,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B353" t="s">
         <v>9</v>
@@ -6966,41 +6977,35 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>598</v>
+        <v>304</v>
       </c>
       <c r="B354" t="s">
-        <v>13</v>
+        <v>240</v>
       </c>
       <c r="C354" t="s">
-        <v>1</v>
-      </c>
-      <c r="D354" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>599</v>
+        <v>305</v>
       </c>
       <c r="B355" t="s">
-        <v>600</v>
+        <v>9</v>
       </c>
       <c r="C355" t="s">
         <v>1</v>
-      </c>
-      <c r="D355" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B356" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C356" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D356" t="s">
         <v>415</v>
@@ -7008,43 +7013,49 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>306</v>
+        <v>599</v>
       </c>
       <c r="B357" t="s">
-        <v>13</v>
+        <v>600</v>
       </c>
       <c r="C357" t="s">
         <v>1</v>
+      </c>
+      <c r="D357" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>307</v>
+        <v>601</v>
       </c>
       <c r="B358" t="s">
-        <v>308</v>
+        <v>4</v>
       </c>
       <c r="C358" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D358" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B359" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C359" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B360" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="C360" t="s">
         <v>1</v>
@@ -7052,21 +7063,21 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B361" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C361" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B362" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C362" t="s">
         <v>1</v>
@@ -7074,24 +7085,21 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>602</v>
+        <v>312</v>
       </c>
       <c r="B363" t="s">
-        <v>603</v>
+        <v>13</v>
       </c>
       <c r="C363" t="s">
         <v>1</v>
-      </c>
-      <c r="D363" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B364" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="C364" t="s">
         <v>1</v>
@@ -7099,32 +7107,35 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>316</v>
+        <v>602</v>
       </c>
       <c r="B365" t="s">
-        <v>91</v>
+        <v>603</v>
       </c>
       <c r="C365" t="s">
         <v>1</v>
+      </c>
+      <c r="D365" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B366" t="s">
-        <v>318</v>
+        <v>9</v>
       </c>
       <c r="C366" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B367" t="s">
-        <v>320</v>
+        <v>91</v>
       </c>
       <c r="C367" t="s">
         <v>1</v>
@@ -7132,21 +7143,21 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B368" t="s">
-        <v>91</v>
+        <v>318</v>
       </c>
       <c r="C368" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B369" t="s">
-        <v>9</v>
+        <v>320</v>
       </c>
       <c r="C369" t="s">
         <v>1</v>
@@ -7154,24 +7165,21 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>604</v>
+        <v>321</v>
       </c>
       <c r="B370" t="s">
-        <v>605</v>
+        <v>91</v>
       </c>
       <c r="C370" t="s">
-        <v>2</v>
-      </c>
-      <c r="D370" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B371" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C371" t="s">
         <v>1</v>
@@ -7179,46 +7187,46 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>324</v>
+        <v>604</v>
       </c>
       <c r="B372" t="s">
-        <v>9</v>
+        <v>605</v>
       </c>
       <c r="C372" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D372" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>606</v>
+        <v>323</v>
       </c>
       <c r="B373" t="s">
-        <v>580</v>
+        <v>13</v>
       </c>
       <c r="C373" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>607</v>
+        <v>324</v>
       </c>
       <c r="B374" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C374" t="s">
-        <v>2</v>
-      </c>
-      <c r="D374" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>325</v>
+        <v>606</v>
       </c>
       <c r="B375" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="C375" t="s">
         <v>2</v>
@@ -7226,7 +7234,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>327</v>
+        <v>607</v>
       </c>
       <c r="B376" t="s">
         <v>20</v>
@@ -7234,35 +7242,38 @@
       <c r="C376" t="s">
         <v>2</v>
       </c>
+      <c r="D376" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B377" t="s">
-        <v>13</v>
+        <v>608</v>
       </c>
       <c r="C377" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B378" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C378" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B379" t="s">
-        <v>609</v>
+        <v>13</v>
       </c>
       <c r="C379" t="s">
         <v>1</v>
@@ -7270,10 +7281,10 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B380" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C380" t="s">
         <v>1</v>
@@ -7281,10 +7292,10 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B381" t="s">
-        <v>13</v>
+        <v>609</v>
       </c>
       <c r="C381" t="s">
         <v>1</v>
@@ -7292,10 +7303,10 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B382" t="s">
-        <v>326</v>
+        <v>6</v>
       </c>
       <c r="C382" t="s">
         <v>1</v>
@@ -7303,24 +7314,21 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>610</v>
+        <v>332</v>
       </c>
       <c r="B383" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C383" t="s">
-        <v>2</v>
-      </c>
-      <c r="D383" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B384" t="s">
-        <v>361</v>
+        <v>326</v>
       </c>
       <c r="C384" t="s">
         <v>1</v>
@@ -7328,32 +7336,32 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>335</v>
+        <v>610</v>
       </c>
       <c r="B385" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C385" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D385" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B386" t="s">
-        <v>9</v>
+        <v>361</v>
       </c>
       <c r="C386" t="s">
         <v>1</v>
-      </c>
-      <c r="D386" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B387" t="s">
         <v>9</v>
@@ -7364,129 +7372,132 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B388" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="C388" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D388" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B389" t="s">
         <v>9</v>
       </c>
       <c r="C389" t="s">
         <v>1</v>
-      </c>
-      <c r="D389" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B390" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C390" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B391" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C391" t="s">
         <v>1</v>
+      </c>
+      <c r="D391" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>426</v>
+        <v>340</v>
       </c>
       <c r="B392" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C392" t="s">
         <v>1</v>
-      </c>
-      <c r="D392" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>420</v>
+        <v>341</v>
       </c>
       <c r="B393" t="s">
-        <v>611</v>
+        <v>13</v>
       </c>
       <c r="C393" t="s">
-        <v>2</v>
-      </c>
-      <c r="D393" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>342</v>
+        <v>426</v>
       </c>
       <c r="B394" t="s">
-        <v>580</v>
+        <v>13</v>
       </c>
       <c r="C394" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D394" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>343</v>
+        <v>420</v>
       </c>
       <c r="B395" t="s">
-        <v>197</v>
+        <v>611</v>
       </c>
       <c r="C395" t="s">
         <v>2</v>
+      </c>
+      <c r="D395" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B396" t="s">
-        <v>9</v>
+        <v>580</v>
       </c>
       <c r="C396" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B397" t="s">
-        <v>11</v>
+        <v>197</v>
       </c>
       <c r="C397" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B398" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C398" t="s">
         <v>1</v>
@@ -7494,60 +7505,60 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>480</v>
+        <v>345</v>
       </c>
       <c r="B399" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C399" t="s">
-        <v>2</v>
-      </c>
-      <c r="D399" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>612</v>
+        <v>346</v>
       </c>
       <c r="B400" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C400" t="s">
-        <v>2</v>
-      </c>
-      <c r="D400" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>347</v>
+        <v>480</v>
       </c>
       <c r="B401" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C401" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D401" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>348</v>
+        <v>612</v>
       </c>
       <c r="B402" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C402" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D402" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B403" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C403" t="s">
         <v>1</v>
@@ -7555,24 +7566,21 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>613</v>
+        <v>348</v>
       </c>
       <c r="B404" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C404" t="s">
-        <v>2</v>
-      </c>
-      <c r="D404" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B405" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C405" t="s">
         <v>1</v>
@@ -7580,13 +7588,13 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B406" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C406" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D406" t="s">
         <v>415</v>
@@ -7594,85 +7602,85 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>493</v>
+        <v>350</v>
       </c>
       <c r="B407" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="C407" t="s">
-        <v>2</v>
-      </c>
-      <c r="D407" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>351</v>
+        <v>614</v>
       </c>
       <c r="B408" t="s">
-        <v>481</v>
+        <v>13</v>
       </c>
       <c r="C408" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D408" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>352</v>
+        <v>493</v>
       </c>
       <c r="B409" t="s">
-        <v>311</v>
+        <v>452</v>
       </c>
       <c r="C409" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D409" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>482</v>
+        <v>351</v>
       </c>
       <c r="B410" t="s">
-        <v>38</v>
+        <v>481</v>
       </c>
       <c r="C410" t="s">
         <v>2</v>
-      </c>
-      <c r="D410" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>615</v>
+        <v>352</v>
       </c>
       <c r="B411" t="s">
-        <v>13</v>
+        <v>311</v>
       </c>
       <c r="C411" t="s">
         <v>1</v>
-      </c>
-      <c r="D411" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>353</v>
+        <v>482</v>
       </c>
       <c r="B412" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C412" t="s">
         <v>2</v>
+      </c>
+      <c r="D412" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B413" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C413" t="s">
         <v>1</v>
@@ -7683,71 +7691,68 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>483</v>
+        <v>353</v>
       </c>
       <c r="B414" t="s">
-        <v>617</v>
+        <v>17</v>
       </c>
       <c r="C414" t="s">
         <v>2</v>
-      </c>
-      <c r="D414" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>354</v>
+        <v>616</v>
       </c>
       <c r="B415" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C415" t="s">
         <v>1</v>
+      </c>
+      <c r="D415" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B416" t="s">
-        <v>355</v>
+        <v>617</v>
       </c>
       <c r="C416" t="s">
         <v>2</v>
+      </c>
+      <c r="D416" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B417" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C417" t="s">
-        <v>2</v>
-      </c>
-      <c r="D417" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>618</v>
+        <v>484</v>
       </c>
       <c r="B418" t="s">
-        <v>13</v>
+        <v>355</v>
       </c>
       <c r="C418" t="s">
-        <v>1</v>
-      </c>
-      <c r="D418" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>619</v>
+        <v>356</v>
       </c>
       <c r="B419" t="s">
         <v>20</v>
@@ -7761,43 +7766,49 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>357</v>
+        <v>618</v>
       </c>
       <c r="B420" t="s">
-        <v>481</v>
+        <v>13</v>
       </c>
       <c r="C420" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D420" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>358</v>
+        <v>619</v>
       </c>
       <c r="B421" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C421" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D421" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B422" t="s">
-        <v>9</v>
+        <v>481</v>
       </c>
       <c r="C422" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B423" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C423" t="s">
         <v>1</v>
@@ -7805,21 +7816,21 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B424" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C424" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B425" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C425" t="s">
         <v>1</v>
@@ -7827,35 +7838,32 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B426" t="s">
-        <v>365</v>
+        <v>20</v>
       </c>
       <c r="C426" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>620</v>
+        <v>363</v>
       </c>
       <c r="B427" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C427" t="s">
         <v>1</v>
-      </c>
-      <c r="D427" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B428" t="s">
-        <v>63</v>
+        <v>365</v>
       </c>
       <c r="C428" t="s">
         <v>1</v>
@@ -7863,32 +7871,32 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>367</v>
+        <v>620</v>
       </c>
       <c r="B429" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C429" t="s">
         <v>1</v>
+      </c>
+      <c r="D429" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>485</v>
+        <v>366</v>
       </c>
       <c r="B430" t="s">
-        <v>486</v>
+        <v>63</v>
       </c>
       <c r="C430" t="s">
-        <v>2</v>
-      </c>
-      <c r="D430" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B431" t="s">
         <v>9</v>
@@ -7899,21 +7907,24 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>369</v>
+        <v>485</v>
       </c>
       <c r="B432" t="s">
-        <v>9</v>
+        <v>486</v>
       </c>
       <c r="C432" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D432" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B433" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C433" t="s">
         <v>1</v>
@@ -7921,7 +7932,7 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B434" t="s">
         <v>9</v>
@@ -7932,7 +7943,7 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B435" t="s">
         <v>13</v>
@@ -7943,60 +7954,60 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>621</v>
+        <v>371</v>
       </c>
       <c r="B436" t="s">
-        <v>622</v>
+        <v>9</v>
       </c>
       <c r="C436" t="s">
         <v>1</v>
-      </c>
-      <c r="D436" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>623</v>
+        <v>372</v>
       </c>
       <c r="B437" t="s">
-        <v>624</v>
+        <v>13</v>
       </c>
       <c r="C437" t="s">
-        <v>2</v>
-      </c>
-      <c r="D437" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>373</v>
+        <v>621</v>
       </c>
       <c r="B438" t="s">
-        <v>55</v>
+        <v>622</v>
       </c>
       <c r="C438" t="s">
         <v>1</v>
+      </c>
+      <c r="D438" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>374</v>
+        <v>623</v>
       </c>
       <c r="B439" t="s">
-        <v>375</v>
+        <v>624</v>
       </c>
       <c r="C439" t="s">
         <v>2</v>
+      </c>
+      <c r="D439" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B440" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="C440" t="s">
         <v>1</v>
@@ -8004,10 +8015,10 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B441" t="s">
-        <v>625</v>
+        <v>375</v>
       </c>
       <c r="C441" t="s">
         <v>2</v>
@@ -8015,10 +8026,10 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B442" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C442" t="s">
         <v>1</v>
@@ -8026,71 +8037,68 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>487</v>
+        <v>377</v>
       </c>
       <c r="B443" t="s">
-        <v>11</v>
+        <v>625</v>
       </c>
       <c r="C443" t="s">
-        <v>1</v>
-      </c>
-      <c r="D443" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B444" t="s">
-        <v>380</v>
+        <v>9</v>
       </c>
       <c r="C444" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>381</v>
+        <v>487</v>
       </c>
       <c r="B445" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C445" t="s">
         <v>1</v>
+      </c>
+      <c r="D445" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B446" t="s">
-        <v>11</v>
+        <v>380</v>
       </c>
       <c r="C446" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>626</v>
+        <v>381</v>
       </c>
       <c r="B447" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C447" t="s">
-        <v>2</v>
-      </c>
-      <c r="D447" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B448" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C448" t="s">
         <v>1</v>
@@ -8098,10 +8106,10 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B449" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C449" t="s">
         <v>2</v>
@@ -8112,18 +8120,18 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B450" t="s">
-        <v>486</v>
+        <v>9</v>
       </c>
       <c r="C450" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>416</v>
+        <v>627</v>
       </c>
       <c r="B451" t="s">
         <v>20</v>
@@ -8131,27 +8139,27 @@
       <c r="C451" t="s">
         <v>2</v>
       </c>
+      <c r="D451" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>628</v>
+        <v>384</v>
       </c>
       <c r="B452" t="s">
-        <v>9</v>
+        <v>486</v>
       </c>
       <c r="C452" t="s">
-        <v>1</v>
-      </c>
-      <c r="D452" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="B453" t="s">
-        <v>488</v>
+        <v>20</v>
       </c>
       <c r="C453" t="s">
         <v>2</v>
@@ -8159,35 +8167,35 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>386</v>
+        <v>628</v>
       </c>
       <c r="B454" t="s">
-        <v>489</v>
+        <v>9</v>
       </c>
       <c r="C454" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D454" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>629</v>
+        <v>385</v>
       </c>
       <c r="B455" t="s">
-        <v>9</v>
+        <v>488</v>
       </c>
       <c r="C455" t="s">
-        <v>1</v>
-      </c>
-      <c r="D455" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>630</v>
+        <v>386</v>
       </c>
       <c r="B456" t="s">
-        <v>631</v>
+        <v>489</v>
       </c>
       <c r="C456" t="s">
         <v>2</v>
@@ -8195,51 +8203,54 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>387</v>
+        <v>629</v>
       </c>
       <c r="B457" t="s">
-        <v>632</v>
+        <v>9</v>
       </c>
       <c r="C457" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D457" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>388</v>
+        <v>630</v>
       </c>
       <c r="B458" t="s">
-        <v>326</v>
+        <v>631</v>
       </c>
       <c r="C458" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B459" t="s">
-        <v>9</v>
+        <v>632</v>
       </c>
       <c r="C459" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B460" t="s">
-        <v>490</v>
+        <v>326</v>
       </c>
       <c r="C460" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B461" t="s">
         <v>9</v>
@@ -8250,21 +8261,21 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B462" t="s">
-        <v>136</v>
+        <v>490</v>
       </c>
       <c r="C462" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>633</v>
+        <v>391</v>
       </c>
       <c r="B463" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C463" t="s">
         <v>1</v>
@@ -8272,10 +8283,10 @@
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B464" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="C464" t="s">
         <v>1</v>
@@ -8283,10 +8294,10 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>394</v>
+        <v>633</v>
       </c>
       <c r="B465" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C465" t="s">
         <v>1</v>
@@ -8294,10 +8305,10 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B466" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C466" t="s">
         <v>1</v>
@@ -8305,10 +8316,10 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B467" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C467" t="s">
         <v>1</v>
@@ -8316,10 +8327,10 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B468" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C468" t="s">
         <v>1</v>
@@ -8327,38 +8338,35 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>634</v>
+        <v>396</v>
       </c>
       <c r="B469" t="s">
         <v>9</v>
       </c>
       <c r="C469" t="s">
         <v>1</v>
-      </c>
-      <c r="D469" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B470" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="C470" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B471" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C471" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D471" t="s">
         <v>415</v>
@@ -8366,32 +8374,35 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B472" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="C472" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>400</v>
+        <v>635</v>
       </c>
       <c r="B473" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C473" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D473" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B474" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C474" t="s">
         <v>1</v>
@@ -8399,10 +8410,10 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B475" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C475" t="s">
         <v>1</v>
@@ -8410,21 +8421,18 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>637</v>
+        <v>401</v>
       </c>
       <c r="B476" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C476" t="s">
-        <v>2</v>
-      </c>
-      <c r="D476" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B477" t="s">
         <v>9</v>
@@ -8435,32 +8443,35 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>404</v>
+        <v>637</v>
       </c>
       <c r="B478" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C478" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D478" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B479" t="s">
-        <v>406</v>
+        <v>9</v>
       </c>
       <c r="C479" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B480" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C480" t="s">
         <v>1</v>
@@ -8468,21 +8479,18 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>638</v>
+        <v>405</v>
       </c>
       <c r="B481" t="s">
-        <v>38</v>
+        <v>406</v>
       </c>
       <c r="C481" t="s">
         <v>2</v>
-      </c>
-      <c r="D481" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B482" t="s">
         <v>9</v>
@@ -8493,29 +8501,54 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>491</v>
+        <v>638</v>
       </c>
       <c r="B483" t="s">
-        <v>492</v>
+        <v>38</v>
       </c>
       <c r="C483" t="s">
         <v>2</v>
+      </c>
+      <c r="D483" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
+        <v>408</v>
+      </c>
+      <c r="B484" t="s">
+        <v>9</v>
+      </c>
+      <c r="C484" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>491</v>
+      </c>
+      <c r="B485" t="s">
+        <v>492</v>
+      </c>
+      <c r="C485" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
         <v>409</v>
       </c>
-      <c r="B484" t="s">
+      <c r="B486" t="s">
         <v>13</v>
       </c>
-      <c r="C484" t="s">
+      <c r="C486" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{8F56ED3D-A3F2-450D-9EAE-1214C3EA2069}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D484">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D486">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>

--- a/assets/guncel_deneme_bonuslari_listesi.xlsx
+++ b/assets/guncel_deneme_bonuslari_listesi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cengi\Desktop\test\Deneme Bonusu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF05BD0-3A3B-4E76-9D50-C85865590EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151D1439-8C94-4A8C-9F19-1EC4CE73B625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD7B2693-F8D1-429F-9AB3-DB64ACA5183F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD7B2693-F8D1-429F-9AB3-DB64ACA5183F}"/>
   </bookViews>
   <sheets>
     <sheet name="guncel_deneme_bonuslari_listesi" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="642">
   <si>
     <t>maks 750tl çekim</t>
   </si>
@@ -1946,6 +1946,9 @@
   </si>
   <si>
     <t>hellocasino</t>
+  </si>
+  <si>
+    <t>minix</t>
   </si>
 </sst>
 </file>
@@ -2835,7 +2838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F56ED3D-A3F2-450D-9EAE-1214C3EA2069}">
-  <dimension ref="A1:D486"/>
+  <dimension ref="A1:D487"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -6773,10 +6776,10 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="B336" t="s">
-        <v>293</v>
+        <v>580</v>
       </c>
       <c r="C336" t="s">
         <v>2</v>
@@ -6787,65 +6790,68 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>288</v>
+        <v>597</v>
       </c>
       <c r="B337" t="s">
-        <v>68</v>
+        <v>293</v>
       </c>
       <c r="C337" t="s">
         <v>2</v>
+      </c>
+      <c r="D337" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B338" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C338" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B339" t="s">
-        <v>466</v>
+        <v>13</v>
       </c>
       <c r="C339" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B340" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C340" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B341" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C341" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B342" t="s">
-        <v>477</v>
+        <v>20</v>
       </c>
       <c r="C342" t="s">
         <v>2</v>
@@ -6853,21 +6859,21 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B343" t="s">
-        <v>55</v>
+        <v>477</v>
       </c>
       <c r="C343" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B344" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="C344" t="s">
         <v>1</v>
@@ -6875,10 +6881,10 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B345" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="C345" t="s">
         <v>1</v>
@@ -6886,68 +6892,68 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B346" t="s">
-        <v>240</v>
+        <v>13</v>
       </c>
       <c r="C346" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B347" t="s">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="C347" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>497</v>
+        <v>299</v>
       </c>
       <c r="B348" t="s">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="C348" t="s">
         <v>1</v>
-      </c>
-      <c r="D348" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>300</v>
+        <v>497</v>
       </c>
       <c r="B349" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C349" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D349" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B350" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C350" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>478</v>
+        <v>301</v>
       </c>
       <c r="B351" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C351" t="s">
         <v>1</v>
@@ -6955,68 +6961,65 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>302</v>
+        <v>478</v>
       </c>
       <c r="B352" t="s">
-        <v>293</v>
+        <v>13</v>
       </c>
       <c r="C352" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B353" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="C353" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B354" t="s">
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="C354" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B355" t="s">
-        <v>9</v>
+        <v>240</v>
       </c>
       <c r="C355" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>598</v>
+        <v>305</v>
       </c>
       <c r="B356" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C356" t="s">
         <v>1</v>
-      </c>
-      <c r="D356" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B357" t="s">
-        <v>600</v>
+        <v>13</v>
       </c>
       <c r="C357" t="s">
         <v>1</v>
@@ -7027,13 +7030,13 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B358" t="s">
-        <v>4</v>
+        <v>600</v>
       </c>
       <c r="C358" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D358" t="s">
         <v>415</v>
@@ -7041,21 +7044,24 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>306</v>
+        <v>601</v>
       </c>
       <c r="B359" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C359" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D359" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B360" t="s">
-        <v>308</v>
+        <v>13</v>
       </c>
       <c r="C360" t="s">
         <v>1</v>
@@ -7063,32 +7069,32 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B361" t="s">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="C361" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B362" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C362" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B363" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C363" t="s">
         <v>1</v>
@@ -7096,10 +7102,10 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B364" t="s">
-        <v>314</v>
+        <v>13</v>
       </c>
       <c r="C364" t="s">
         <v>1</v>
@@ -7107,35 +7113,35 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>602</v>
+        <v>313</v>
       </c>
       <c r="B365" t="s">
-        <v>603</v>
+        <v>314</v>
       </c>
       <c r="C365" t="s">
         <v>1</v>
-      </c>
-      <c r="D365" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>315</v>
+        <v>602</v>
       </c>
       <c r="B366" t="s">
-        <v>9</v>
+        <v>603</v>
       </c>
       <c r="C366" t="s">
         <v>1</v>
+      </c>
+      <c r="D366" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B367" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="C367" t="s">
         <v>1</v>
@@ -7143,32 +7149,32 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B368" t="s">
-        <v>318</v>
+        <v>91</v>
       </c>
       <c r="C368" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B369" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C369" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B370" t="s">
-        <v>91</v>
+        <v>320</v>
       </c>
       <c r="C370" t="s">
         <v>1</v>
@@ -7176,10 +7182,10 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B371" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="C371" t="s">
         <v>1</v>
@@ -7187,35 +7193,35 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>604</v>
+        <v>322</v>
       </c>
       <c r="B372" t="s">
-        <v>605</v>
+        <v>9</v>
       </c>
       <c r="C372" t="s">
-        <v>2</v>
-      </c>
-      <c r="D372" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>323</v>
+        <v>604</v>
       </c>
       <c r="B373" t="s">
-        <v>13</v>
+        <v>605</v>
       </c>
       <c r="C373" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D373" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B374" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C374" t="s">
         <v>1</v>
@@ -7223,46 +7229,46 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>606</v>
+        <v>324</v>
       </c>
       <c r="B375" t="s">
-        <v>580</v>
+        <v>9</v>
       </c>
       <c r="C375" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B376" t="s">
-        <v>20</v>
+        <v>580</v>
       </c>
       <c r="C376" t="s">
         <v>2</v>
-      </c>
-      <c r="D376" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>325</v>
+        <v>607</v>
       </c>
       <c r="B377" t="s">
-        <v>608</v>
+        <v>20</v>
       </c>
       <c r="C377" t="s">
         <v>2</v>
+      </c>
+      <c r="D377" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B378" t="s">
-        <v>20</v>
+        <v>608</v>
       </c>
       <c r="C378" t="s">
         <v>2</v>
@@ -7270,21 +7276,21 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B379" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C379" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B380" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C380" t="s">
         <v>1</v>
@@ -7292,10 +7298,10 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B381" t="s">
-        <v>609</v>
+        <v>0</v>
       </c>
       <c r="C381" t="s">
         <v>1</v>
@@ -7303,10 +7309,10 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B382" t="s">
-        <v>6</v>
+        <v>609</v>
       </c>
       <c r="C382" t="s">
         <v>1</v>
@@ -7314,10 +7320,10 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B383" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C383" t="s">
         <v>1</v>
@@ -7325,10 +7331,10 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B384" t="s">
-        <v>326</v>
+        <v>13</v>
       </c>
       <c r="C384" t="s">
         <v>1</v>
@@ -7336,35 +7342,35 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>610</v>
+        <v>333</v>
       </c>
       <c r="B385" t="s">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="C385" t="s">
-        <v>2</v>
-      </c>
-      <c r="D385" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>334</v>
+        <v>610</v>
       </c>
       <c r="B386" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="C386" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D386" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B387" t="s">
-        <v>9</v>
+        <v>361</v>
       </c>
       <c r="C387" t="s">
         <v>1</v>
@@ -7372,71 +7378,71 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B388" t="s">
         <v>9</v>
       </c>
       <c r="C388" t="s">
         <v>1</v>
-      </c>
-      <c r="D388" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B389" t="s">
         <v>9</v>
       </c>
       <c r="C389" t="s">
         <v>1</v>
+      </c>
+      <c r="D389" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B390" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="C390" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B391" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C391" t="s">
-        <v>1</v>
-      </c>
-      <c r="D391" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B392" t="s">
         <v>9</v>
       </c>
       <c r="C392" t="s">
         <v>1</v>
+      </c>
+      <c r="D392" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B393" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C393" t="s">
         <v>1</v>
@@ -7444,7 +7450,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>426</v>
+        <v>341</v>
       </c>
       <c r="B394" t="s">
         <v>13</v>
@@ -7452,19 +7458,16 @@
       <c r="C394" t="s">
         <v>1</v>
       </c>
-      <c r="D394" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B395" t="s">
-        <v>611</v>
+        <v>13</v>
       </c>
       <c r="C395" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D395" t="s">
         <v>415</v>
@@ -7472,21 +7475,24 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>342</v>
+        <v>420</v>
       </c>
       <c r="B396" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="C396" t="s">
         <v>2</v>
+      </c>
+      <c r="D396" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B397" t="s">
-        <v>197</v>
+        <v>580</v>
       </c>
       <c r="C397" t="s">
         <v>2</v>
@@ -7494,21 +7500,21 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B398" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="C398" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B399" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C399" t="s">
         <v>1</v>
@@ -7516,10 +7522,10 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B400" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C400" t="s">
         <v>1</v>
@@ -7527,21 +7533,18 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>480</v>
+        <v>346</v>
       </c>
       <c r="B401" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C401" t="s">
-        <v>2</v>
-      </c>
-      <c r="D401" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>612</v>
+        <v>480</v>
       </c>
       <c r="B402" t="s">
         <v>38</v>
@@ -7555,21 +7558,24 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>347</v>
+        <v>612</v>
       </c>
       <c r="B403" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C403" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D403" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B404" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C404" t="s">
         <v>1</v>
@@ -7577,7 +7583,7 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B405" t="s">
         <v>13</v>
@@ -7588,52 +7594,49 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>613</v>
+        <v>349</v>
       </c>
       <c r="B406" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C406" t="s">
-        <v>2</v>
-      </c>
-      <c r="D406" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>350</v>
+        <v>613</v>
       </c>
       <c r="B407" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C407" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D407" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>614</v>
+        <v>350</v>
       </c>
       <c r="B408" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C408" t="s">
         <v>1</v>
-      </c>
-      <c r="D408" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>493</v>
+        <v>614</v>
       </c>
       <c r="B409" t="s">
-        <v>452</v>
+        <v>13</v>
       </c>
       <c r="C409" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D409" t="s">
         <v>415</v>
@@ -7641,49 +7644,49 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>351</v>
+        <v>493</v>
       </c>
       <c r="B410" t="s">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="C410" t="s">
         <v>2</v>
+      </c>
+      <c r="D410" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B411" t="s">
-        <v>311</v>
+        <v>481</v>
       </c>
       <c r="C411" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>482</v>
+        <v>352</v>
       </c>
       <c r="B412" t="s">
-        <v>38</v>
+        <v>311</v>
       </c>
       <c r="C412" t="s">
-        <v>2</v>
-      </c>
-      <c r="D412" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>615</v>
+        <v>482</v>
       </c>
       <c r="B413" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C413" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D413" t="s">
         <v>415</v>
@@ -7691,38 +7694,38 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>353</v>
+        <v>615</v>
       </c>
       <c r="B414" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C414" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D414" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>616</v>
+        <v>353</v>
       </c>
       <c r="B415" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C415" t="s">
-        <v>1</v>
-      </c>
-      <c r="D415" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>483</v>
+        <v>616</v>
       </c>
       <c r="B416" t="s">
-        <v>617</v>
+        <v>9</v>
       </c>
       <c r="C416" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D416" t="s">
         <v>415</v>
@@ -7730,49 +7733,49 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>354</v>
+        <v>483</v>
       </c>
       <c r="B417" t="s">
-        <v>13</v>
+        <v>617</v>
       </c>
       <c r="C417" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D417" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>484</v>
+        <v>354</v>
       </c>
       <c r="B418" t="s">
-        <v>355</v>
+        <v>13</v>
       </c>
       <c r="C418" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>356</v>
+        <v>484</v>
       </c>
       <c r="B419" t="s">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="C419" t="s">
         <v>2</v>
-      </c>
-      <c r="D419" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>618</v>
+        <v>356</v>
       </c>
       <c r="B420" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C420" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D420" t="s">
         <v>415</v>
@@ -7780,13 +7783,13 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B421" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C421" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D421" t="s">
         <v>415</v>
@@ -7794,32 +7797,35 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>357</v>
+        <v>619</v>
       </c>
       <c r="B422" t="s">
-        <v>481</v>
+        <v>20</v>
       </c>
       <c r="C422" t="s">
         <v>2</v>
+      </c>
+      <c r="D422" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B423" t="s">
-        <v>13</v>
+        <v>481</v>
       </c>
       <c r="C423" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B424" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C424" t="s">
         <v>1</v>
@@ -7827,10 +7833,10 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B425" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C425" t="s">
         <v>1</v>
@@ -7838,32 +7844,32 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B426" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C426" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B427" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C427" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B428" t="s">
-        <v>365</v>
+        <v>13</v>
       </c>
       <c r="C428" t="s">
         <v>1</v>
@@ -7871,35 +7877,35 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>620</v>
+        <v>364</v>
       </c>
       <c r="B429" t="s">
-        <v>38</v>
+        <v>365</v>
       </c>
       <c r="C429" t="s">
         <v>1</v>
-      </c>
-      <c r="D429" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>366</v>
+        <v>620</v>
       </c>
       <c r="B430" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="C430" t="s">
         <v>1</v>
+      </c>
+      <c r="D430" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B431" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C431" t="s">
         <v>1</v>
@@ -7907,32 +7913,32 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>485</v>
+        <v>367</v>
       </c>
       <c r="B432" t="s">
-        <v>486</v>
+        <v>9</v>
       </c>
       <c r="C432" t="s">
-        <v>2</v>
-      </c>
-      <c r="D432" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>368</v>
+        <v>485</v>
       </c>
       <c r="B433" t="s">
-        <v>9</v>
+        <v>486</v>
       </c>
       <c r="C433" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D433" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B434" t="s">
         <v>9</v>
@@ -7943,10 +7949,10 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B435" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C435" t="s">
         <v>1</v>
@@ -7954,10 +7960,10 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B436" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C436" t="s">
         <v>1</v>
@@ -7965,10 +7971,10 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B437" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C437" t="s">
         <v>1</v>
@@ -7976,27 +7982,24 @@
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>621</v>
+        <v>372</v>
       </c>
       <c r="B438" t="s">
-        <v>622</v>
+        <v>13</v>
       </c>
       <c r="C438" t="s">
         <v>1</v>
-      </c>
-      <c r="D438" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B439" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C439" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D439" t="s">
         <v>415</v>
@@ -8004,101 +8007,104 @@
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>373</v>
+        <v>623</v>
       </c>
       <c r="B440" t="s">
-        <v>55</v>
+        <v>624</v>
       </c>
       <c r="C440" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D440" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B441" t="s">
-        <v>375</v>
+        <v>55</v>
       </c>
       <c r="C441" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B442" t="s">
-        <v>13</v>
+        <v>375</v>
       </c>
       <c r="C442" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B443" t="s">
-        <v>625</v>
+        <v>13</v>
       </c>
       <c r="C443" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B444" t="s">
-        <v>9</v>
+        <v>625</v>
       </c>
       <c r="C444" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>487</v>
+        <v>378</v>
       </c>
       <c r="B445" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C445" t="s">
         <v>1</v>
-      </c>
-      <c r="D445" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="B446" t="s">
-        <v>380</v>
+        <v>11</v>
       </c>
       <c r="C446" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D446" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B447" t="s">
-        <v>9</v>
+        <v>380</v>
       </c>
       <c r="C447" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B448" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C448" t="s">
         <v>1</v>
@@ -8106,60 +8112,60 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>626</v>
+        <v>382</v>
       </c>
       <c r="B449" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C449" t="s">
-        <v>2</v>
-      </c>
-      <c r="D449" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>383</v>
+        <v>626</v>
       </c>
       <c r="B450" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C450" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D450" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>627</v>
+        <v>383</v>
       </c>
       <c r="B451" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C451" t="s">
-        <v>2</v>
-      </c>
-      <c r="D451" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>384</v>
+        <v>627</v>
       </c>
       <c r="B452" t="s">
-        <v>486</v>
+        <v>20</v>
       </c>
       <c r="C452" t="s">
         <v>2</v>
+      </c>
+      <c r="D452" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="B453" t="s">
-        <v>20</v>
+        <v>486</v>
       </c>
       <c r="C453" t="s">
         <v>2</v>
@@ -8167,35 +8173,35 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>628</v>
+        <v>416</v>
       </c>
       <c r="B454" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C454" t="s">
-        <v>1</v>
-      </c>
-      <c r="D454" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>385</v>
+        <v>628</v>
       </c>
       <c r="B455" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C455" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D455" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B456" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C456" t="s">
         <v>2</v>
@@ -8203,35 +8209,35 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>629</v>
+        <v>386</v>
       </c>
       <c r="B457" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="C457" t="s">
-        <v>1</v>
-      </c>
-      <c r="D457" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B458" t="s">
-        <v>631</v>
+        <v>9</v>
       </c>
       <c r="C458" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D458" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>387</v>
+        <v>630</v>
       </c>
       <c r="B459" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C459" t="s">
         <v>2</v>
@@ -8239,21 +8245,21 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B460" t="s">
-        <v>326</v>
+        <v>632</v>
       </c>
       <c r="C460" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B461" t="s">
-        <v>9</v>
+        <v>326</v>
       </c>
       <c r="C461" t="s">
         <v>1</v>
@@ -8261,32 +8267,32 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B462" t="s">
-        <v>490</v>
+        <v>9</v>
       </c>
       <c r="C462" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B463" t="s">
-        <v>9</v>
+        <v>490</v>
       </c>
       <c r="C463" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B464" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C464" t="s">
         <v>1</v>
@@ -8294,10 +8300,10 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>633</v>
+        <v>392</v>
       </c>
       <c r="B465" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="C465" t="s">
         <v>1</v>
@@ -8305,10 +8311,10 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>393</v>
+        <v>633</v>
       </c>
       <c r="B466" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C466" t="s">
         <v>1</v>
@@ -8316,7 +8322,7 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B467" t="s">
         <v>13</v>
@@ -8327,10 +8333,10 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B468" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C468" t="s">
         <v>1</v>
@@ -8338,10 +8344,10 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B469" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C469" t="s">
         <v>1</v>
@@ -8349,7 +8355,7 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B470" t="s">
         <v>9</v>
@@ -8360,60 +8366,60 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>634</v>
+        <v>397</v>
       </c>
       <c r="B471" t="s">
         <v>9</v>
       </c>
       <c r="C471" t="s">
         <v>1</v>
-      </c>
-      <c r="D471" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>398</v>
+        <v>634</v>
       </c>
       <c r="B472" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="C472" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D472" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>635</v>
+        <v>398</v>
       </c>
       <c r="B473" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C473" t="s">
         <v>2</v>
-      </c>
-      <c r="D473" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>399</v>
+        <v>635</v>
       </c>
       <c r="B474" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C474" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D474" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B475" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C475" t="s">
         <v>1</v>
@@ -8421,10 +8427,10 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B476" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C476" t="s">
         <v>1</v>
@@ -8432,7 +8438,7 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B477" t="s">
         <v>9</v>
@@ -8443,35 +8449,35 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>637</v>
+        <v>402</v>
       </c>
       <c r="B478" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C478" t="s">
-        <v>2</v>
-      </c>
-      <c r="D478" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>403</v>
+        <v>637</v>
       </c>
       <c r="B479" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C479" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D479" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B480" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C480" t="s">
         <v>1</v>
@@ -8479,70 +8485,81 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B481" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="C481" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B482" t="s">
-        <v>9</v>
+        <v>406</v>
       </c>
       <c r="C482" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>638</v>
+        <v>407</v>
       </c>
       <c r="B483" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C483" t="s">
-        <v>2</v>
-      </c>
-      <c r="D483" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>408</v>
+        <v>638</v>
       </c>
       <c r="B484" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C484" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D484" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>491</v>
+        <v>408</v>
       </c>
       <c r="B485" t="s">
-        <v>492</v>
+        <v>9</v>
       </c>
       <c r="C485" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
+        <v>491</v>
+      </c>
+      <c r="B486" t="s">
+        <v>492</v>
+      </c>
+      <c r="C486" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
         <v>409</v>
       </c>
-      <c r="B486" t="s">
+      <c r="B487" t="s">
         <v>13</v>
       </c>
-      <c r="C486" t="s">
+      <c r="C487" t="s">
         <v>1</v>
       </c>
     </row>

--- a/assets/guncel_deneme_bonuslari_listesi.xlsx
+++ b/assets/guncel_deneme_bonuslari_listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cengi\Desktop\test\Deneme Bonusu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151D1439-8C94-4A8C-9F19-1EC4CE73B625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73709E62-6A9E-47A0-B30C-DDBD336AA353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD7B2693-F8D1-429F-9AB3-DB64ACA5183F}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="649">
   <si>
     <t>maks 750tl çekim</t>
   </si>
@@ -1949,6 +1949,27 @@
   </si>
   <si>
     <t>minix</t>
+  </si>
+  <si>
+    <t>casiwin</t>
+  </si>
+  <si>
+    <t>Min 1k. Bakiyenin %10 u kadar çekim</t>
+  </si>
+  <si>
+    <t>galatacasino</t>
+  </si>
+  <si>
+    <t>goldenpalace</t>
+  </si>
+  <si>
+    <t>Çekim kadar yatırım. Sınır yok.</t>
+  </si>
+  <si>
+    <t>probet</t>
+  </si>
+  <si>
+    <t>tempo365</t>
   </si>
 </sst>
 </file>
@@ -2838,7 +2859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F56ED3D-A3F2-450D-9EAE-1214C3EA2069}">
-  <dimension ref="A1:D487"/>
+  <dimension ref="A1:D492"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -4833,13 +4854,13 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>151</v>
+        <v>642</v>
       </c>
       <c r="B170" t="s">
-        <v>548</v>
+        <v>643</v>
       </c>
       <c r="C170" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170" t="s">
         <v>415</v>
@@ -4847,32 +4868,35 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B171" t="s">
-        <v>68</v>
+        <v>548</v>
       </c>
       <c r="C171" t="s">
         <v>2</v>
+      </c>
+      <c r="D171" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B172" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C172" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B173" t="s">
-        <v>549</v>
+        <v>13</v>
       </c>
       <c r="C173" t="s">
         <v>1</v>
@@ -4880,46 +4904,46 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B174" t="s">
-        <v>20</v>
+        <v>549</v>
       </c>
       <c r="C174" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>421</v>
+        <v>155</v>
       </c>
       <c r="B175" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C175" t="s">
-        <v>1</v>
-      </c>
-      <c r="D175" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>156</v>
+        <v>421</v>
       </c>
       <c r="B176" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C176" t="s">
         <v>1</v>
+      </c>
+      <c r="D176" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B177" t="s">
-        <v>456</v>
+        <v>9</v>
       </c>
       <c r="C177" t="s">
         <v>1</v>
@@ -4927,35 +4951,35 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>457</v>
+        <v>157</v>
       </c>
       <c r="B178" t="s">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="C178" t="s">
-        <v>2</v>
-      </c>
-      <c r="D178" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>158</v>
+        <v>457</v>
       </c>
       <c r="B179" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C179" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D179" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B180" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C180" t="s">
         <v>1</v>
@@ -4963,10 +4987,10 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B181" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="C181" t="s">
         <v>1</v>
@@ -4974,71 +4998,71 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B182" t="s">
-        <v>550</v>
+        <v>91</v>
       </c>
       <c r="C182" t="s">
-        <v>2</v>
-      </c>
-      <c r="D182" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B183" t="s">
-        <v>13</v>
+        <v>550</v>
       </c>
       <c r="C183" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D183" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>636</v>
+        <v>162</v>
       </c>
       <c r="B184" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C184" t="s">
         <v>1</v>
-      </c>
-      <c r="D184" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>163</v>
+        <v>636</v>
       </c>
       <c r="B185" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C185" t="s">
         <v>1</v>
+      </c>
+      <c r="D185" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>458</v>
+        <v>163</v>
       </c>
       <c r="B186" t="s">
-        <v>459</v>
+        <v>13</v>
       </c>
       <c r="C186" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>582</v>
+        <v>458</v>
       </c>
       <c r="B187" t="s">
-        <v>583</v>
+        <v>459</v>
       </c>
       <c r="C187" t="s">
         <v>2</v>
@@ -5046,10 +5070,10 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>164</v>
+        <v>582</v>
       </c>
       <c r="B188" t="s">
-        <v>165</v>
+        <v>583</v>
       </c>
       <c r="C188" t="s">
         <v>2</v>
@@ -5057,10 +5081,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B189" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="C189" t="s">
         <v>2</v>
@@ -5068,57 +5092,57 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>460</v>
+        <v>166</v>
       </c>
       <c r="B190" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C190" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B191" t="s">
-        <v>462</v>
+        <v>11</v>
       </c>
       <c r="C191" t="s">
-        <v>2</v>
-      </c>
-      <c r="D191" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>167</v>
+        <v>461</v>
       </c>
       <c r="B192" t="s">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="C192" t="s">
         <v>2</v>
+      </c>
+      <c r="D192" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B193" t="s">
-        <v>9</v>
+        <v>551</v>
       </c>
       <c r="C193" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B194" t="s">
-        <v>552</v>
+        <v>9</v>
       </c>
       <c r="C194" t="s">
         <v>1</v>
@@ -5126,10 +5150,10 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B195" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C195" t="s">
         <v>1</v>
@@ -5137,68 +5161,68 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B196" t="s">
-        <v>172</v>
+        <v>553</v>
       </c>
       <c r="C196" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B197" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="C197" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>554</v>
+        <v>173</v>
       </c>
       <c r="B198" t="s">
         <v>9</v>
       </c>
       <c r="C198" t="s">
         <v>1</v>
-      </c>
-      <c r="D198" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>174</v>
+        <v>554</v>
       </c>
       <c r="B199" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C199" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D199" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B200" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C200" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B201" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C201" t="s">
         <v>1</v>
@@ -5206,79 +5230,79 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>555</v>
+        <v>176</v>
       </c>
       <c r="B202" t="s">
-        <v>556</v>
+        <v>9</v>
       </c>
       <c r="C202" t="s">
         <v>1</v>
-      </c>
-      <c r="D202" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>463</v>
+        <v>555</v>
       </c>
       <c r="B203" t="s">
-        <v>479</v>
+        <v>556</v>
       </c>
       <c r="C203" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D203" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>177</v>
+        <v>463</v>
       </c>
       <c r="B204" t="s">
-        <v>558</v>
+        <v>479</v>
       </c>
       <c r="C204" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>559</v>
+        <v>177</v>
       </c>
       <c r="B205" t="s">
-        <v>9</v>
+        <v>558</v>
       </c>
       <c r="C205" t="s">
         <v>1</v>
-      </c>
-      <c r="D205" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>178</v>
+        <v>559</v>
       </c>
       <c r="B206" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C206" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D206" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B207" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C207" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B208" t="s">
         <v>13</v>
@@ -5289,7 +5313,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>424</v>
+        <v>180</v>
       </c>
       <c r="B209" t="s">
         <v>13</v>
@@ -5297,118 +5321,121 @@
       <c r="C209" t="s">
         <v>1</v>
       </c>
-      <c r="D209" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>181</v>
+        <v>424</v>
       </c>
       <c r="B210" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C210" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D210" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B211" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C211" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B212" t="s">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="C212" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="B213" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="C213" t="s">
-        <v>1</v>
-      </c>
-      <c r="D213" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>464</v>
+        <v>560</v>
       </c>
       <c r="B214" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C214" t="s">
         <v>1</v>
+      </c>
+      <c r="D214" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B215" t="s">
-        <v>466</v>
+        <v>9</v>
       </c>
       <c r="C215" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>185</v>
+        <v>465</v>
       </c>
       <c r="B216" t="s">
-        <v>13</v>
+        <v>466</v>
       </c>
       <c r="C216" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>186</v>
+        <v>644</v>
       </c>
       <c r="B217" t="s">
-        <v>187</v>
+        <v>361</v>
       </c>
       <c r="C217" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D217" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>467</v>
+        <v>185</v>
       </c>
       <c r="B218" t="s">
-        <v>548</v>
+        <v>13</v>
       </c>
       <c r="C218" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B219" t="s">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="C219" t="s">
         <v>2</v>
@@ -5416,63 +5443,57 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>189</v>
+        <v>467</v>
       </c>
       <c r="B220" t="s">
-        <v>30</v>
+        <v>548</v>
       </c>
       <c r="C220" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B221" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C221" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>561</v>
+        <v>189</v>
       </c>
       <c r="B222" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C222" t="s">
-        <v>2</v>
-      </c>
-      <c r="D222" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>562</v>
+        <v>190</v>
       </c>
       <c r="B223" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C223" t="s">
-        <v>2</v>
-      </c>
-      <c r="D223" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B224" t="s">
-        <v>564</v>
+        <v>38</v>
       </c>
       <c r="C224" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D224" t="s">
         <v>415</v>
@@ -5480,68 +5501,71 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>191</v>
+        <v>562</v>
       </c>
       <c r="B225" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C225" t="s">
         <v>2</v>
+      </c>
+      <c r="D225" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>192</v>
+        <v>563</v>
       </c>
       <c r="B226" t="s">
-        <v>77</v>
+        <v>564</v>
       </c>
       <c r="C226" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D226" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B227" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C227" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B228" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="C228" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>423</v>
+        <v>193</v>
       </c>
       <c r="B229" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C229" t="s">
-        <v>2</v>
-      </c>
-      <c r="D229" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B230" t="s">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="C230" t="s">
         <v>1</v>
@@ -5549,32 +5573,38 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>196</v>
+        <v>423</v>
       </c>
       <c r="B231" t="s">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="C231" t="s">
         <v>2</v>
+      </c>
+      <c r="D231" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>198</v>
+        <v>645</v>
       </c>
       <c r="B232" t="s">
-        <v>20</v>
+        <v>646</v>
       </c>
       <c r="C232" t="s">
         <v>2</v>
+      </c>
+      <c r="D232" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B233" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C233" t="s">
         <v>1</v>
@@ -5582,10 +5612,10 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B234" t="s">
-        <v>468</v>
+        <v>197</v>
       </c>
       <c r="C234" t="s">
         <v>2</v>
@@ -5593,24 +5623,21 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>566</v>
+        <v>198</v>
       </c>
       <c r="B235" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="C235" t="s">
-        <v>1</v>
-      </c>
-      <c r="D235" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B236" t="s">
-        <v>257</v>
+        <v>9</v>
       </c>
       <c r="C236" t="s">
         <v>1</v>
@@ -5618,24 +5645,21 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>567</v>
+        <v>200</v>
       </c>
       <c r="B237" t="s">
-        <v>568</v>
+        <v>468</v>
       </c>
       <c r="C237" t="s">
         <v>2</v>
-      </c>
-      <c r="D237" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B238" t="s">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="C238" t="s">
         <v>1</v>
@@ -5646,10 +5670,10 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B239" t="s">
-        <v>93</v>
+        <v>257</v>
       </c>
       <c r="C239" t="s">
         <v>1</v>
@@ -5657,21 +5681,24 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>203</v>
+        <v>567</v>
       </c>
       <c r="B240" t="s">
-        <v>254</v>
+        <v>568</v>
       </c>
       <c r="C240" t="s">
         <v>2</v>
+      </c>
+      <c r="D240" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>640</v>
+        <v>569</v>
       </c>
       <c r="B241" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C241" t="s">
         <v>1</v>
@@ -5682,10 +5709,10 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>469</v>
+        <v>202</v>
       </c>
       <c r="B242" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="C242" t="s">
         <v>1</v>
@@ -5693,10 +5720,10 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B243" t="s">
-        <v>570</v>
+        <v>254</v>
       </c>
       <c r="C243" t="s">
         <v>2</v>
@@ -5704,18 +5731,21 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>205</v>
+        <v>640</v>
       </c>
       <c r="B244" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C244" t="s">
         <v>1</v>
+      </c>
+      <c r="D244" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>206</v>
+        <v>469</v>
       </c>
       <c r="B245" t="s">
         <v>13</v>
@@ -5726,10 +5756,10 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B246" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C246" t="s">
         <v>2</v>
@@ -5737,7 +5767,7 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B247" t="s">
         <v>9</v>
@@ -5748,32 +5778,32 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B248" t="s">
-        <v>557</v>
+        <v>13</v>
       </c>
       <c r="C248" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B249" t="s">
-        <v>211</v>
+        <v>571</v>
       </c>
       <c r="C249" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B250" t="s">
-        <v>572</v>
+        <v>9</v>
       </c>
       <c r="C250" t="s">
         <v>1</v>
@@ -5781,10 +5811,10 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B251" t="s">
-        <v>214</v>
+        <v>557</v>
       </c>
       <c r="C251" t="s">
         <v>2</v>
@@ -5792,10 +5822,10 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B252" t="s">
-        <v>573</v>
+        <v>211</v>
       </c>
       <c r="C252" t="s">
         <v>1</v>
@@ -5803,93 +5833,93 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B253" t="s">
-        <v>20</v>
+        <v>572</v>
       </c>
       <c r="C253" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>574</v>
+        <v>213</v>
       </c>
       <c r="B254" t="s">
-        <v>38</v>
+        <v>214</v>
       </c>
       <c r="C254" t="s">
         <v>2</v>
-      </c>
-      <c r="D254" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B255" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="C255" t="s">
-        <v>2</v>
-      </c>
-      <c r="D255" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B256" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C256" t="s">
-        <v>1</v>
-      </c>
-      <c r="D256" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>219</v>
+        <v>574</v>
       </c>
       <c r="B257" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C257" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D257" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B258" t="s">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="C258" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D258" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B259" t="s">
         <v>9</v>
       </c>
       <c r="C259" t="s">
         <v>1</v>
+      </c>
+      <c r="D259" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B260" t="s">
         <v>9</v>
@@ -5900,32 +5930,29 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>575</v>
+        <v>220</v>
       </c>
       <c r="B261" t="s">
-        <v>38</v>
+        <v>221</v>
       </c>
       <c r="C261" t="s">
-        <v>2</v>
-      </c>
-      <c r="D261" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>470</v>
+        <v>222</v>
       </c>
       <c r="B262" t="s">
-        <v>197</v>
+        <v>9</v>
       </c>
       <c r="C262" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B263" t="s">
         <v>9</v>
@@ -5936,21 +5963,24 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>225</v>
+        <v>575</v>
       </c>
       <c r="B264" t="s">
-        <v>576</v>
+        <v>38</v>
       </c>
       <c r="C264" t="s">
         <v>2</v>
+      </c>
+      <c r="D264" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>226</v>
+        <v>470</v>
       </c>
       <c r="B265" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="C265" t="s">
         <v>2</v>
@@ -5958,46 +5988,43 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B266" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C266" t="s">
         <v>1</v>
-      </c>
-      <c r="D266" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>422</v>
+        <v>225</v>
       </c>
       <c r="B267" t="s">
-        <v>9</v>
+        <v>576</v>
       </c>
       <c r="C267" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B268" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="C268" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>577</v>
+        <v>227</v>
       </c>
       <c r="B269" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C269" t="s">
         <v>1</v>
@@ -6008,65 +6035,65 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>229</v>
+        <v>422</v>
       </c>
       <c r="B270" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C270" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>471</v>
+        <v>228</v>
       </c>
       <c r="B271" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C271" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>230</v>
+        <v>577</v>
       </c>
       <c r="B272" t="s">
         <v>9</v>
       </c>
       <c r="C272" t="s">
         <v>1</v>
+      </c>
+      <c r="D272" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B273" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C273" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>578</v>
+        <v>471</v>
       </c>
       <c r="B274" t="s">
-        <v>579</v>
+        <v>20</v>
       </c>
       <c r="C274" t="s">
-        <v>1</v>
-      </c>
-      <c r="D274" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>472</v>
+        <v>230</v>
       </c>
       <c r="B275" t="s">
         <v>9</v>
@@ -6077,29 +6104,32 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B276" t="s">
-        <v>580</v>
+        <v>11</v>
       </c>
       <c r="C276" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>233</v>
+        <v>578</v>
       </c>
       <c r="B277" t="s">
-        <v>13</v>
+        <v>579</v>
       </c>
       <c r="C277" t="s">
         <v>1</v>
+      </c>
+      <c r="D277" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>234</v>
+        <v>472</v>
       </c>
       <c r="B278" t="s">
         <v>9</v>
@@ -6110,57 +6140,51 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B279" t="s">
-        <v>93</v>
+        <v>580</v>
       </c>
       <c r="C279" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B280" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C280" t="s">
         <v>1</v>
-      </c>
-      <c r="D280" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>584</v>
+        <v>234</v>
       </c>
       <c r="B281" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C281" t="s">
         <v>1</v>
-      </c>
-      <c r="D281" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B282" t="s">
-        <v>238</v>
+        <v>93</v>
       </c>
       <c r="C282" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>585</v>
+        <v>236</v>
       </c>
       <c r="B283" t="s">
         <v>9</v>
@@ -6174,46 +6198,49 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>239</v>
+        <v>584</v>
       </c>
       <c r="B284" t="s">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="C284" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D284" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>586</v>
+        <v>237</v>
       </c>
       <c r="B285" t="s">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="C285" t="s">
-        <v>1</v>
-      </c>
-      <c r="D285" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>241</v>
+        <v>585</v>
       </c>
       <c r="B286" t="s">
-        <v>242</v>
+        <v>9</v>
       </c>
       <c r="C286" t="s">
         <v>1</v>
+      </c>
+      <c r="D286" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B287" t="s">
-        <v>102</v>
+        <v>240</v>
       </c>
       <c r="C287" t="s">
         <v>2</v>
@@ -6221,21 +6248,24 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>244</v>
+        <v>586</v>
       </c>
       <c r="B288" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="C288" t="s">
         <v>1</v>
+      </c>
+      <c r="D288" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B289" t="s">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="C289" t="s">
         <v>1</v>
@@ -6243,10 +6273,10 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B290" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C290" t="s">
         <v>2</v>
@@ -6254,35 +6284,32 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B291" t="s">
-        <v>197</v>
+        <v>13</v>
       </c>
       <c r="C291" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>428</v>
+        <v>245</v>
       </c>
       <c r="B292" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C292" t="s">
         <v>1</v>
-      </c>
-      <c r="D292" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B293" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="C293" t="s">
         <v>2</v>
@@ -6290,10 +6317,10 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B294" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="C294" t="s">
         <v>2</v>
@@ -6301,21 +6328,24 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>251</v>
+        <v>428</v>
       </c>
       <c r="B295" t="s">
-        <v>252</v>
+        <v>9</v>
       </c>
       <c r="C295" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D295" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B296" t="s">
-        <v>254</v>
+        <v>38</v>
       </c>
       <c r="C296" t="s">
         <v>2</v>
@@ -6323,63 +6353,60 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>587</v>
+        <v>249</v>
       </c>
       <c r="B297" t="s">
-        <v>9</v>
+        <v>250</v>
       </c>
       <c r="C297" t="s">
-        <v>1</v>
-      </c>
-      <c r="D297" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>425</v>
+        <v>251</v>
       </c>
       <c r="B298" t="s">
-        <v>9</v>
+        <v>252</v>
       </c>
       <c r="C298" t="s">
-        <v>1</v>
-      </c>
-      <c r="D298" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B299" t="s">
-        <v>13</v>
+        <v>254</v>
       </c>
       <c r="C299" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>256</v>
+        <v>587</v>
       </c>
       <c r="B300" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C300" t="s">
         <v>1</v>
+      </c>
+      <c r="D300" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>588</v>
+        <v>425</v>
       </c>
       <c r="B301" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C301" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D301" t="s">
         <v>415</v>
@@ -6387,7 +6414,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B302" t="s">
         <v>13</v>
@@ -6398,24 +6425,24 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B303" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C303" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B304" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C304" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D304" t="s">
         <v>415</v>
@@ -6423,10 +6450,10 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B305" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C305" t="s">
         <v>1</v>
@@ -6434,32 +6461,35 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B306" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C306" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>262</v>
+        <v>589</v>
       </c>
       <c r="B307" t="s">
         <v>9</v>
       </c>
       <c r="C307" t="s">
         <v>1</v>
+      </c>
+      <c r="D307" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B308" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C308" t="s">
         <v>1</v>
@@ -6467,18 +6497,18 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B309" t="s">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="C309" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B310" t="s">
         <v>9</v>
@@ -6489,10 +6519,10 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B311" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C311" t="s">
         <v>1</v>
@@ -6500,10 +6530,10 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B312" t="s">
-        <v>268</v>
+        <v>197</v>
       </c>
       <c r="C312" t="s">
         <v>2</v>
@@ -6511,21 +6541,21 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B313" t="s">
-        <v>270</v>
+        <v>9</v>
       </c>
       <c r="C313" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B314" t="s">
-        <v>272</v>
+        <v>9</v>
       </c>
       <c r="C314" t="s">
         <v>1</v>
@@ -6533,35 +6563,32 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>590</v>
+        <v>267</v>
       </c>
       <c r="B315" t="s">
-        <v>55</v>
+        <v>268</v>
       </c>
       <c r="C315" t="s">
-        <v>1</v>
-      </c>
-      <c r="D315" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B316" t="s">
-        <v>9</v>
+        <v>270</v>
       </c>
       <c r="C316" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B317" t="s">
-        <v>13</v>
+        <v>272</v>
       </c>
       <c r="C317" t="s">
         <v>1</v>
@@ -6569,21 +6596,24 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>473</v>
+        <v>590</v>
       </c>
       <c r="B318" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C318" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D318" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B319" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C319" t="s">
         <v>1</v>
@@ -6591,57 +6621,54 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>591</v>
+        <v>275</v>
       </c>
       <c r="B320" t="s">
-        <v>592</v>
+        <v>13</v>
       </c>
       <c r="C320" t="s">
-        <v>2</v>
-      </c>
-      <c r="D320" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>277</v>
+        <v>473</v>
       </c>
       <c r="B321" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="C321" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>593</v>
+        <v>276</v>
       </c>
       <c r="B322" t="s">
-        <v>594</v>
+        <v>55</v>
       </c>
       <c r="C322" t="s">
-        <v>2</v>
-      </c>
-      <c r="D322" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>278</v>
+        <v>591</v>
       </c>
       <c r="B323" t="s">
-        <v>9</v>
+        <v>592</v>
       </c>
       <c r="C323" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D323" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B324" t="s">
         <v>9</v>
@@ -6652,18 +6679,21 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>280</v>
+        <v>593</v>
       </c>
       <c r="B325" t="s">
-        <v>30</v>
+        <v>594</v>
       </c>
       <c r="C325" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D325" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B326" t="s">
         <v>9</v>
@@ -6674,7 +6704,7 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B327" t="s">
         <v>9</v>
@@ -6685,65 +6715,65 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>474</v>
+        <v>280</v>
       </c>
       <c r="B328" t="s">
-        <v>452</v>
+        <v>30</v>
       </c>
       <c r="C328" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>475</v>
+        <v>281</v>
       </c>
       <c r="B329" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C329" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B330" t="s">
-        <v>273</v>
+        <v>9</v>
       </c>
       <c r="C330" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>284</v>
+        <v>474</v>
       </c>
       <c r="B331" t="s">
-        <v>9</v>
+        <v>452</v>
       </c>
       <c r="C331" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>285</v>
+        <v>475</v>
       </c>
       <c r="B332" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C332" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B333" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C333" t="s">
         <v>2</v>
@@ -6751,24 +6781,21 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>595</v>
+        <v>284</v>
       </c>
       <c r="B334" t="s">
-        <v>596</v>
+        <v>9</v>
       </c>
       <c r="C334" t="s">
         <v>1</v>
-      </c>
-      <c r="D334" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>476</v>
+        <v>285</v>
       </c>
       <c r="B335" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C335" t="s">
         <v>1</v>
@@ -6776,27 +6803,24 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>641</v>
+        <v>286</v>
       </c>
       <c r="B336" t="s">
-        <v>580</v>
+        <v>287</v>
       </c>
       <c r="C336" t="s">
         <v>2</v>
-      </c>
-      <c r="D336" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B337" t="s">
-        <v>293</v>
+        <v>596</v>
       </c>
       <c r="C337" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D337" t="s">
         <v>415</v>
@@ -6804,65 +6828,71 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="B338" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C338" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>289</v>
+        <v>641</v>
       </c>
       <c r="B339" t="s">
-        <v>13</v>
+        <v>580</v>
       </c>
       <c r="C339" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D339" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>290</v>
+        <v>597</v>
       </c>
       <c r="B340" t="s">
-        <v>466</v>
+        <v>293</v>
       </c>
       <c r="C340" t="s">
         <v>2</v>
+      </c>
+      <c r="D340" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B341" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C341" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B342" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C342" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B343" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C343" t="s">
         <v>2</v>
@@ -6870,10 +6900,10 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B344" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C344" t="s">
         <v>1</v>
@@ -6881,40 +6911,40 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B345" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="C345" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B346" t="s">
-        <v>13</v>
+        <v>477</v>
       </c>
       <c r="C346" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B347" t="s">
-        <v>240</v>
+        <v>55</v>
       </c>
       <c r="C347" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B348" t="s">
         <v>136</v>
@@ -6925,24 +6955,21 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>497</v>
+        <v>297</v>
       </c>
       <c r="B349" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C349" t="s">
         <v>1</v>
-      </c>
-      <c r="D349" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B350" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="C350" t="s">
         <v>2</v>
@@ -6950,10 +6977,10 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B351" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="C351" t="s">
         <v>1</v>
@@ -6961,21 +6988,24 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="B352" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C352" t="s">
         <v>1</v>
+      </c>
+      <c r="D352" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B353" t="s">
-        <v>293</v>
+        <v>20</v>
       </c>
       <c r="C353" t="s">
         <v>2</v>
@@ -6983,10 +7013,10 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B354" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C354" t="s">
         <v>1</v>
@@ -6994,71 +7024,62 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>304</v>
+        <v>478</v>
       </c>
       <c r="B355" t="s">
-        <v>240</v>
+        <v>13</v>
       </c>
       <c r="C355" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B356" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="C356" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>598</v>
+        <v>303</v>
       </c>
       <c r="B357" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C357" t="s">
         <v>1</v>
-      </c>
-      <c r="D357" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>599</v>
+        <v>304</v>
       </c>
       <c r="B358" t="s">
-        <v>600</v>
+        <v>240</v>
       </c>
       <c r="C358" t="s">
-        <v>1</v>
-      </c>
-      <c r="D358" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>601</v>
+        <v>305</v>
       </c>
       <c r="B359" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C359" t="s">
-        <v>2</v>
-      </c>
-      <c r="D359" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>306</v>
+        <v>598</v>
       </c>
       <c r="B360" t="s">
         <v>13</v>
@@ -7066,35 +7087,44 @@
       <c r="C360" t="s">
         <v>1</v>
       </c>
+      <c r="D360" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>307</v>
+        <v>599</v>
       </c>
       <c r="B361" t="s">
-        <v>308</v>
+        <v>600</v>
       </c>
       <c r="C361" t="s">
         <v>1</v>
+      </c>
+      <c r="D361" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>309</v>
+        <v>601</v>
       </c>
       <c r="B362" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C362" t="s">
         <v>2</v>
+      </c>
+      <c r="D362" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B363" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C363" t="s">
         <v>1</v>
@@ -7102,10 +7132,10 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B364" t="s">
-        <v>13</v>
+        <v>308</v>
       </c>
       <c r="C364" t="s">
         <v>1</v>
@@ -7113,35 +7143,32 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B365" t="s">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="C365" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>602</v>
+        <v>310</v>
       </c>
       <c r="B366" t="s">
-        <v>603</v>
+        <v>9</v>
       </c>
       <c r="C366" t="s">
         <v>1</v>
-      </c>
-      <c r="D366" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B367" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C367" t="s">
         <v>1</v>
@@ -7149,10 +7176,10 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B368" t="s">
-        <v>91</v>
+        <v>314</v>
       </c>
       <c r="C368" t="s">
         <v>1</v>
@@ -7160,21 +7187,24 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>317</v>
+        <v>602</v>
       </c>
       <c r="B369" t="s">
-        <v>318</v>
+        <v>603</v>
       </c>
       <c r="C369" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D369" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B370" t="s">
-        <v>320</v>
+        <v>9</v>
       </c>
       <c r="C370" t="s">
         <v>1</v>
@@ -7182,7 +7212,7 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B371" t="s">
         <v>91</v>
@@ -7193,35 +7223,32 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B372" t="s">
-        <v>9</v>
+        <v>318</v>
       </c>
       <c r="C372" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>604</v>
+        <v>319</v>
       </c>
       <c r="B373" t="s">
-        <v>605</v>
+        <v>320</v>
       </c>
       <c r="C373" t="s">
-        <v>2</v>
-      </c>
-      <c r="D373" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B374" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="C374" t="s">
         <v>1</v>
@@ -7229,7 +7256,7 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B375" t="s">
         <v>9</v>
@@ -7240,46 +7267,46 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B376" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="C376" t="s">
         <v>2</v>
+      </c>
+      <c r="D376" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>607</v>
+        <v>323</v>
       </c>
       <c r="B377" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C377" t="s">
-        <v>2</v>
-      </c>
-      <c r="D377" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B378" t="s">
-        <v>608</v>
+        <v>9</v>
       </c>
       <c r="C378" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>327</v>
+        <v>606</v>
       </c>
       <c r="B379" t="s">
-        <v>20</v>
+        <v>580</v>
       </c>
       <c r="C379" t="s">
         <v>2</v>
@@ -7287,43 +7314,46 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>328</v>
+        <v>607</v>
       </c>
       <c r="B380" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C380" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D380" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B381" t="s">
-        <v>0</v>
+        <v>608</v>
       </c>
       <c r="C381" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B382" t="s">
-        <v>609</v>
+        <v>20</v>
       </c>
       <c r="C382" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B383" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C383" t="s">
         <v>1</v>
@@ -7331,10 +7361,10 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B384" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C384" t="s">
         <v>1</v>
@@ -7342,35 +7372,35 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>333</v>
+        <v>647</v>
       </c>
       <c r="B385" t="s">
-        <v>326</v>
+        <v>466</v>
       </c>
       <c r="C385" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D385" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>610</v>
+        <v>330</v>
       </c>
       <c r="B386" t="s">
-        <v>20</v>
+        <v>609</v>
       </c>
       <c r="C386" t="s">
-        <v>2</v>
-      </c>
-      <c r="D386" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B387" t="s">
-        <v>361</v>
+        <v>6</v>
       </c>
       <c r="C387" t="s">
         <v>1</v>
@@ -7378,10 +7408,10 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B388" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C388" t="s">
         <v>1</v>
@@ -7389,71 +7419,71 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B389" t="s">
-        <v>9</v>
+        <v>326</v>
       </c>
       <c r="C389" t="s">
         <v>1</v>
-      </c>
-      <c r="D389" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>337</v>
+        <v>610</v>
       </c>
       <c r="B390" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C390" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D390" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B391" t="s">
-        <v>72</v>
+        <v>361</v>
       </c>
       <c r="C391" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B392" t="s">
         <v>9</v>
       </c>
       <c r="C392" t="s">
         <v>1</v>
-      </c>
-      <c r="D392" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B393" t="s">
         <v>9</v>
       </c>
       <c r="C393" t="s">
         <v>1</v>
+      </c>
+      <c r="D393" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B394" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C394" t="s">
         <v>1</v>
@@ -7461,27 +7491,24 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>426</v>
+        <v>338</v>
       </c>
       <c r="B395" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="C395" t="s">
-        <v>1</v>
-      </c>
-      <c r="D395" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>420</v>
+        <v>339</v>
       </c>
       <c r="B396" t="s">
-        <v>611</v>
+        <v>9</v>
       </c>
       <c r="C396" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D396" t="s">
         <v>415</v>
@@ -7489,93 +7516,93 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B397" t="s">
-        <v>580</v>
+        <v>9</v>
       </c>
       <c r="C397" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B398" t="s">
-        <v>197</v>
+        <v>13</v>
       </c>
       <c r="C398" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>344</v>
+        <v>426</v>
       </c>
       <c r="B399" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C399" t="s">
         <v>1</v>
+      </c>
+      <c r="D399" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>345</v>
+        <v>420</v>
       </c>
       <c r="B400" t="s">
-        <v>11</v>
+        <v>611</v>
       </c>
       <c r="C400" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D400" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B401" t="s">
-        <v>28</v>
+        <v>580</v>
       </c>
       <c r="C401" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>480</v>
+        <v>343</v>
       </c>
       <c r="B402" t="s">
-        <v>38</v>
+        <v>197</v>
       </c>
       <c r="C402" t="s">
         <v>2</v>
-      </c>
-      <c r="D402" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>612</v>
+        <v>344</v>
       </c>
       <c r="B403" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C403" t="s">
-        <v>2</v>
-      </c>
-      <c r="D403" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B404" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C404" t="s">
         <v>1</v>
@@ -7583,10 +7610,10 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B405" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C405" t="s">
         <v>1</v>
@@ -7594,21 +7621,24 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>349</v>
+        <v>480</v>
       </c>
       <c r="B406" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C406" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D406" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B407" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C407" t="s">
         <v>2</v>
@@ -7619,10 +7649,10 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B408" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C408" t="s">
         <v>1</v>
@@ -7630,7 +7660,7 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>614</v>
+        <v>348</v>
       </c>
       <c r="B409" t="s">
         <v>13</v>
@@ -7638,41 +7668,38 @@
       <c r="C409" t="s">
         <v>1</v>
       </c>
-      <c r="D409" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>493</v>
+        <v>349</v>
       </c>
       <c r="B410" t="s">
-        <v>452</v>
+        <v>13</v>
       </c>
       <c r="C410" t="s">
-        <v>2</v>
-      </c>
-      <c r="D410" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>351</v>
+        <v>613</v>
       </c>
       <c r="B411" t="s">
-        <v>481</v>
+        <v>68</v>
       </c>
       <c r="C411" t="s">
         <v>2</v>
+      </c>
+      <c r="D411" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B412" t="s">
-        <v>311</v>
+        <v>30</v>
       </c>
       <c r="C412" t="s">
         <v>1</v>
@@ -7680,13 +7707,13 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>482</v>
+        <v>614</v>
       </c>
       <c r="B413" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C413" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D413" t="s">
         <v>415</v>
@@ -7694,13 +7721,13 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>615</v>
+        <v>493</v>
       </c>
       <c r="B414" t="s">
-        <v>13</v>
+        <v>452</v>
       </c>
       <c r="C414" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D414" t="s">
         <v>415</v>
@@ -7708,10 +7735,10 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B415" t="s">
-        <v>17</v>
+        <v>481</v>
       </c>
       <c r="C415" t="s">
         <v>2</v>
@@ -7719,24 +7746,21 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>616</v>
+        <v>352</v>
       </c>
       <c r="B416" t="s">
-        <v>9</v>
+        <v>311</v>
       </c>
       <c r="C416" t="s">
         <v>1</v>
-      </c>
-      <c r="D416" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B417" t="s">
-        <v>617</v>
+        <v>38</v>
       </c>
       <c r="C417" t="s">
         <v>2</v>
@@ -7747,7 +7771,7 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>354</v>
+        <v>615</v>
       </c>
       <c r="B418" t="s">
         <v>13</v>
@@ -7755,13 +7779,16 @@
       <c r="C418" t="s">
         <v>1</v>
       </c>
+      <c r="D418" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>484</v>
+        <v>353</v>
       </c>
       <c r="B419" t="s">
-        <v>355</v>
+        <v>17</v>
       </c>
       <c r="C419" t="s">
         <v>2</v>
@@ -7769,13 +7796,13 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>356</v>
+        <v>616</v>
       </c>
       <c r="B420" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C420" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D420" t="s">
         <v>415</v>
@@ -7783,13 +7810,13 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>618</v>
+        <v>483</v>
       </c>
       <c r="B421" t="s">
-        <v>13</v>
+        <v>617</v>
       </c>
       <c r="C421" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D421" t="s">
         <v>415</v>
@@ -7797,24 +7824,21 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>619</v>
+        <v>354</v>
       </c>
       <c r="B422" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C422" t="s">
-        <v>2</v>
-      </c>
-      <c r="D422" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>357</v>
+        <v>484</v>
       </c>
       <c r="B423" t="s">
-        <v>481</v>
+        <v>355</v>
       </c>
       <c r="C423" t="s">
         <v>2</v>
@@ -7822,43 +7846,52 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B424" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C424" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D424" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>359</v>
+        <v>618</v>
       </c>
       <c r="B425" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C425" t="s">
         <v>1</v>
+      </c>
+      <c r="D425" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>360</v>
+        <v>619</v>
       </c>
       <c r="B426" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C426" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D426" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B427" t="s">
-        <v>20</v>
+        <v>481</v>
       </c>
       <c r="C427" t="s">
         <v>2</v>
@@ -7866,7 +7899,7 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B428" t="s">
         <v>13</v>
@@ -7877,10 +7910,10 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B429" t="s">
-        <v>365</v>
+        <v>9</v>
       </c>
       <c r="C429" t="s">
         <v>1</v>
@@ -7888,35 +7921,32 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>620</v>
+        <v>360</v>
       </c>
       <c r="B430" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C430" t="s">
         <v>1</v>
-      </c>
-      <c r="D430" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B431" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="C431" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B432" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C432" t="s">
         <v>1</v>
@@ -7924,35 +7954,35 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>485</v>
+        <v>364</v>
       </c>
       <c r="B433" t="s">
-        <v>486</v>
+        <v>365</v>
       </c>
       <c r="C433" t="s">
-        <v>2</v>
-      </c>
-      <c r="D433" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>368</v>
+        <v>620</v>
       </c>
       <c r="B434" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C434" t="s">
         <v>1</v>
+      </c>
+      <c r="D434" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B435" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C435" t="s">
         <v>1</v>
@@ -7960,10 +7990,10 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B436" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C436" t="s">
         <v>1</v>
@@ -7971,21 +8001,24 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>371</v>
+        <v>485</v>
       </c>
       <c r="B437" t="s">
-        <v>9</v>
+        <v>486</v>
       </c>
       <c r="C437" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D437" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B438" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C438" t="s">
         <v>1</v>
@@ -7993,57 +8026,54 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>621</v>
+        <v>369</v>
       </c>
       <c r="B439" t="s">
-        <v>622</v>
+        <v>9</v>
       </c>
       <c r="C439" t="s">
         <v>1</v>
-      </c>
-      <c r="D439" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>623</v>
+        <v>370</v>
       </c>
       <c r="B440" t="s">
-        <v>624</v>
+        <v>13</v>
       </c>
       <c r="C440" t="s">
-        <v>2</v>
-      </c>
-      <c r="D440" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>373</v>
+        <v>648</v>
       </c>
       <c r="B441" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C441" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D441" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B442" t="s">
-        <v>375</v>
+        <v>9</v>
       </c>
       <c r="C442" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B443" t="s">
         <v>13</v>
@@ -8054,46 +8084,49 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>377</v>
+        <v>621</v>
       </c>
       <c r="B444" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C444" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D444" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>378</v>
+        <v>623</v>
       </c>
       <c r="B445" t="s">
-        <v>9</v>
+        <v>624</v>
       </c>
       <c r="C445" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D445" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>487</v>
+        <v>373</v>
       </c>
       <c r="B446" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="C446" t="s">
         <v>1</v>
-      </c>
-      <c r="D446" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B447" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C447" t="s">
         <v>2</v>
@@ -8101,10 +8134,10 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B448" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C448" t="s">
         <v>1</v>
@@ -8112,85 +8145,82 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B449" t="s">
-        <v>11</v>
+        <v>625</v>
       </c>
       <c r="C449" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>626</v>
+        <v>378</v>
       </c>
       <c r="B450" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C450" t="s">
-        <v>2</v>
-      </c>
-      <c r="D450" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>383</v>
+        <v>487</v>
       </c>
       <c r="B451" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C451" t="s">
         <v>1</v>
+      </c>
+      <c r="D451" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>627</v>
+        <v>379</v>
       </c>
       <c r="B452" t="s">
-        <v>20</v>
+        <v>380</v>
       </c>
       <c r="C452" t="s">
         <v>2</v>
-      </c>
-      <c r="D452" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B453" t="s">
-        <v>486</v>
+        <v>9</v>
       </c>
       <c r="C453" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>416</v>
+        <v>382</v>
       </c>
       <c r="B454" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C454" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B455" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C455" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D455" t="s">
         <v>415</v>
@@ -8198,46 +8228,46 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B456" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C456" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>386</v>
+        <v>627</v>
       </c>
       <c r="B457" t="s">
-        <v>489</v>
+        <v>20</v>
       </c>
       <c r="C457" t="s">
         <v>2</v>
+      </c>
+      <c r="D457" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>629</v>
+        <v>384</v>
       </c>
       <c r="B458" t="s">
-        <v>9</v>
+        <v>486</v>
       </c>
       <c r="C458" t="s">
-        <v>1</v>
-      </c>
-      <c r="D458" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>630</v>
+        <v>416</v>
       </c>
       <c r="B459" t="s">
-        <v>631</v>
+        <v>20</v>
       </c>
       <c r="C459" t="s">
         <v>2</v>
@@ -8245,76 +8275,82 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>387</v>
+        <v>628</v>
       </c>
       <c r="B460" t="s">
-        <v>632</v>
+        <v>9</v>
       </c>
       <c r="C460" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D460" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B461" t="s">
-        <v>326</v>
+        <v>488</v>
       </c>
       <c r="C461" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B462" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="C462" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>390</v>
+        <v>629</v>
       </c>
       <c r="B463" t="s">
-        <v>490</v>
+        <v>9</v>
       </c>
       <c r="C463" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D463" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>391</v>
+        <v>630</v>
       </c>
       <c r="B464" t="s">
-        <v>9</v>
+        <v>631</v>
       </c>
       <c r="C464" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B465" t="s">
-        <v>136</v>
+        <v>632</v>
       </c>
       <c r="C465" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>633</v>
+        <v>388</v>
       </c>
       <c r="B466" t="s">
-        <v>11</v>
+        <v>326</v>
       </c>
       <c r="C466" t="s">
         <v>1</v>
@@ -8322,10 +8358,10 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B467" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C467" t="s">
         <v>1</v>
@@ -8333,21 +8369,21 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B468" t="s">
-        <v>13</v>
+        <v>490</v>
       </c>
       <c r="C468" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B469" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C469" t="s">
         <v>1</v>
@@ -8355,10 +8391,10 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B470" t="s">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="C470" t="s">
         <v>1</v>
@@ -8366,10 +8402,10 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>397</v>
+        <v>633</v>
       </c>
       <c r="B471" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C471" t="s">
         <v>1</v>
@@ -8377,49 +8413,43 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>634</v>
+        <v>393</v>
       </c>
       <c r="B472" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C472" t="s">
         <v>1</v>
-      </c>
-      <c r="D472" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B473" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="C473" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>635</v>
+        <v>395</v>
       </c>
       <c r="B474" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C474" t="s">
-        <v>2</v>
-      </c>
-      <c r="D474" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B475" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C475" t="s">
         <v>1</v>
@@ -8427,10 +8457,10 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B476" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C476" t="s">
         <v>1</v>
@@ -8438,29 +8468,32 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>401</v>
+        <v>634</v>
       </c>
       <c r="B477" t="s">
         <v>9</v>
       </c>
       <c r="C477" t="s">
         <v>1</v>
+      </c>
+      <c r="D477" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B478" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="C478" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B479" t="s">
         <v>38</v>
@@ -8474,10 +8507,10 @@
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B480" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C480" t="s">
         <v>1</v>
@@ -8485,10 +8518,10 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B481" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C481" t="s">
         <v>1</v>
@@ -8496,18 +8529,18 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B482" t="s">
-        <v>406</v>
+        <v>9</v>
       </c>
       <c r="C482" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B483" t="s">
         <v>9</v>
@@ -8518,7 +8551,7 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B484" t="s">
         <v>38</v>
@@ -8532,7 +8565,7 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B485" t="s">
         <v>9</v>
@@ -8543,29 +8576,87 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>491</v>
+        <v>404</v>
       </c>
       <c r="B486" t="s">
-        <v>492</v>
+        <v>13</v>
       </c>
       <c r="C486" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
+        <v>405</v>
+      </c>
+      <c r="B487" t="s">
+        <v>406</v>
+      </c>
+      <c r="C487" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>407</v>
+      </c>
+      <c r="B488" t="s">
+        <v>9</v>
+      </c>
+      <c r="C488" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>638</v>
+      </c>
+      <c r="B489" t="s">
+        <v>38</v>
+      </c>
+      <c r="C489" t="s">
+        <v>2</v>
+      </c>
+      <c r="D489" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>408</v>
+      </c>
+      <c r="B490" t="s">
+        <v>9</v>
+      </c>
+      <c r="C490" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>491</v>
+      </c>
+      <c r="B491" t="s">
+        <v>492</v>
+      </c>
+      <c r="C491" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
         <v>409</v>
       </c>
-      <c r="B487" t="s">
+      <c r="B492" t="s">
         <v>13</v>
       </c>
-      <c r="C487" t="s">
+      <c r="C492" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{8F56ED3D-A3F2-450D-9EAE-1214C3EA2069}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D486">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D492">
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>

--- a/assets/guncel_deneme_bonuslari_listesi.xlsx
+++ b/assets/guncel_deneme_bonuslari_listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cengi\Desktop\test\Deneme Bonusu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73709E62-6A9E-47A0-B30C-DDBD336AA353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E42686B-9E0F-4719-BF61-240F6C73BA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD7B2693-F8D1-429F-9AB3-DB64ACA5183F}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="guncel_deneme_bonuslari_listesi" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guncel_deneme_bonuslari_listesi!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guncel_deneme_bonuslari_listesi!$A$1:$D$492</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="651">
   <si>
     <t>maks 750tl çekim</t>
   </si>
@@ -1970,6 +1970,12 @@
   </si>
   <si>
     <t>tempo365</t>
+  </si>
+  <si>
+    <t>betpuf</t>
+  </si>
+  <si>
+    <t>Maks 200tl hesaba geçer. Yatırım sonrası kullanılabilir.</t>
   </si>
 </sst>
 </file>
@@ -2859,7 +2865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F56ED3D-A3F2-450D-9EAE-1214C3EA2069}">
-  <dimension ref="A1:D492"/>
+  <dimension ref="A1:D493"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -4182,21 +4188,24 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>110</v>
+        <v>649</v>
       </c>
       <c r="B113" t="s">
-        <v>441</v>
+        <v>650</v>
       </c>
       <c r="C113" t="s">
         <v>2</v>
+      </c>
+      <c r="D113" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="C114" t="s">
         <v>2</v>
@@ -4204,7 +4213,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B115" t="s">
         <v>20</v>
@@ -4215,21 +4224,21 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="C116" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B117" t="s">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="C117" t="s">
         <v>1</v>
@@ -4237,7 +4246,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B118" t="s">
         <v>9</v>
@@ -4248,10 +4257,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C119" t="s">
         <v>1</v>
@@ -4259,10 +4268,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -4270,10 +4279,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="C121" t="s">
         <v>1</v>
@@ -4281,7 +4290,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
@@ -4292,10 +4301,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
         <v>1</v>
@@ -4303,143 +4312,140 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C124" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="C125" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C126" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C127" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>534</v>
+        <v>127</v>
       </c>
       <c r="B128" t="s">
         <v>9</v>
       </c>
       <c r="C128" t="s">
         <v>1</v>
-      </c>
-      <c r="D128" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>128</v>
+        <v>534</v>
       </c>
       <c r="B129" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C129" t="s">
         <v>1</v>
+      </c>
+      <c r="D129" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>535</v>
+        <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>535</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C131" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>536</v>
+        <v>129</v>
       </c>
       <c r="B132" t="s">
         <v>9</v>
       </c>
       <c r="C132" t="s">
         <v>1</v>
-      </c>
-      <c r="D132" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>536</v>
       </c>
       <c r="B133" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C133" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D133" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>419</v>
+        <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C134" t="s">
-        <v>1</v>
-      </c>
-      <c r="D134" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>537</v>
+        <v>419</v>
       </c>
       <c r="B135" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C135" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135" t="s">
         <v>415</v>
@@ -4447,21 +4453,24 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>447</v>
+        <v>537</v>
       </c>
       <c r="B136" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C136" t="s">
         <v>2</v>
+      </c>
+      <c r="D136" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>131</v>
+        <v>447</v>
       </c>
       <c r="B137" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C137" t="s">
         <v>2</v>
@@ -4469,10 +4478,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B138" t="s">
-        <v>538</v>
+        <v>20</v>
       </c>
       <c r="C138" t="s">
         <v>2</v>
@@ -4480,10 +4489,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B139" t="s">
-        <v>38</v>
+        <v>538</v>
       </c>
       <c r="C139" t="s">
         <v>2</v>
@@ -4491,10 +4500,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B140" t="s">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="C140" t="s">
         <v>2</v>
@@ -4502,21 +4511,21 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>448</v>
+        <v>134</v>
       </c>
       <c r="B141" t="s">
-        <v>539</v>
+        <v>102</v>
       </c>
       <c r="C141" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>135</v>
+        <v>448</v>
       </c>
       <c r="B142" t="s">
-        <v>30</v>
+        <v>539</v>
       </c>
       <c r="C142" t="s">
         <v>1</v>
@@ -4524,10 +4533,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B143" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="C143" t="s">
         <v>1</v>
@@ -4535,7 +4544,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B144" t="s">
         <v>136</v>
@@ -4546,63 +4555,60 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>540</v>
+        <v>138</v>
       </c>
       <c r="B145" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="C145" t="s">
         <v>1</v>
-      </c>
-      <c r="D145" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>540</v>
       </c>
       <c r="B146" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C146" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D146" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B147" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C147" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>427</v>
+        <v>140</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C148" t="s">
         <v>1</v>
-      </c>
-      <c r="D148" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>496</v>
+        <v>427</v>
       </c>
       <c r="B149" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C149" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" t="s">
         <v>415</v>
@@ -4610,32 +4616,35 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>141</v>
+        <v>496</v>
       </c>
       <c r="B150" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C150" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D150" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B151" t="s">
-        <v>449</v>
+        <v>9</v>
       </c>
       <c r="C151" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B152" t="s">
-        <v>38</v>
+        <v>449</v>
       </c>
       <c r="C152" t="s">
         <v>2</v>
@@ -4643,10 +4652,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>450</v>
+        <v>143</v>
       </c>
       <c r="B153" t="s">
-        <v>451</v>
+        <v>38</v>
       </c>
       <c r="C153" t="s">
         <v>2</v>
@@ -4654,32 +4663,32 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>541</v>
+        <v>450</v>
       </c>
       <c r="B154" t="s">
-        <v>38</v>
+        <v>451</v>
       </c>
       <c r="C154" t="s">
         <v>2</v>
-      </c>
-      <c r="D154" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>144</v>
+        <v>541</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C155" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D155" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>639</v>
+        <v>144</v>
       </c>
       <c r="B156" t="s">
         <v>13</v>
@@ -4687,27 +4696,27 @@
       <c r="C156" t="s">
         <v>1</v>
       </c>
-      <c r="D156" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>542</v>
+        <v>639</v>
       </c>
       <c r="B157" t="s">
-        <v>543</v>
+        <v>13</v>
       </c>
       <c r="C157" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D157" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>145</v>
+        <v>542</v>
       </c>
       <c r="B158" t="s">
-        <v>146</v>
+        <v>543</v>
       </c>
       <c r="C158" t="s">
         <v>2</v>
@@ -4715,24 +4724,21 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>544</v>
+        <v>145</v>
       </c>
       <c r="B159" t="s">
-        <v>9</v>
+        <v>146</v>
       </c>
       <c r="C159" t="s">
-        <v>1</v>
-      </c>
-      <c r="D159" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>417</v>
+        <v>544</v>
       </c>
       <c r="B160" t="s">
-        <v>545</v>
+        <v>9</v>
       </c>
       <c r="C160" t="s">
         <v>1</v>
@@ -4743,13 +4749,13 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>546</v>
+        <v>417</v>
       </c>
       <c r="B161" t="s">
-        <v>38</v>
+        <v>545</v>
       </c>
       <c r="C161" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D161" t="s">
         <v>415</v>
@@ -4757,10 +4763,10 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>147</v>
+        <v>546</v>
       </c>
       <c r="B162" t="s">
-        <v>453</v>
+        <v>38</v>
       </c>
       <c r="C162" t="s">
         <v>2</v>
@@ -4771,18 +4777,21 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B163" t="s">
-        <v>9</v>
+        <v>453</v>
       </c>
       <c r="C163" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D163" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B164" t="s">
         <v>9</v>
@@ -4793,7 +4802,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>454</v>
+        <v>149</v>
       </c>
       <c r="B165" t="s">
         <v>9</v>
@@ -4804,24 +4813,21 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="B166" t="s">
-        <v>257</v>
+        <v>9</v>
       </c>
       <c r="C166" t="s">
         <v>1</v>
-      </c>
-      <c r="D166" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B167" t="s">
-        <v>547</v>
+        <v>257</v>
       </c>
       <c r="C167" t="s">
         <v>1</v>
@@ -4832,21 +4838,24 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>150</v>
+        <v>418</v>
       </c>
       <c r="B168" t="s">
-        <v>13</v>
+        <v>547</v>
       </c>
       <c r="C168" t="s">
         <v>1</v>
+      </c>
+      <c r="D168" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>455</v>
+        <v>150</v>
       </c>
       <c r="B169" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C169" t="s">
         <v>1</v>
@@ -4854,27 +4863,24 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>642</v>
+        <v>455</v>
       </c>
       <c r="B170" t="s">
-        <v>643</v>
+        <v>9</v>
       </c>
       <c r="C170" t="s">
         <v>1</v>
-      </c>
-      <c r="D170" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>151</v>
+        <v>642</v>
       </c>
       <c r="B171" t="s">
-        <v>548</v>
+        <v>643</v>
       </c>
       <c r="C171" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D171" t="s">
         <v>415</v>
@@ -4882,32 +4888,35 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B172" t="s">
-        <v>68</v>
+        <v>548</v>
       </c>
       <c r="C172" t="s">
         <v>2</v>
+      </c>
+      <c r="D172" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B173" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C173" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B174" t="s">
-        <v>549</v>
+        <v>13</v>
       </c>
       <c r="C174" t="s">
         <v>1</v>
@@ -4915,46 +4924,46 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B175" t="s">
-        <v>20</v>
+        <v>549</v>
       </c>
       <c r="C175" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>421</v>
+        <v>155</v>
       </c>
       <c r="B176" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C176" t="s">
-        <v>1</v>
-      </c>
-      <c r="D176" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>156</v>
+        <v>421</v>
       </c>
       <c r="B177" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C177" t="s">
         <v>1</v>
+      </c>
+      <c r="D177" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B178" t="s">
-        <v>456</v>
+        <v>9</v>
       </c>
       <c r="C178" t="s">
         <v>1</v>
@@ -4962,35 +4971,35 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>457</v>
+        <v>157</v>
       </c>
       <c r="B179" t="s">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="C179" t="s">
-        <v>2</v>
-      </c>
-      <c r="D179" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>158</v>
+        <v>457</v>
       </c>
       <c r="B180" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C180" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D180" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B181" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C181" t="s">
         <v>1</v>
@@ -4998,10 +5007,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B182" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="C182" t="s">
         <v>1</v>
@@ -5009,71 +5018,71 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B183" t="s">
-        <v>550</v>
+        <v>91</v>
       </c>
       <c r="C183" t="s">
-        <v>2</v>
-      </c>
-      <c r="D183" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B184" t="s">
-        <v>13</v>
+        <v>550</v>
       </c>
       <c r="C184" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D184" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>636</v>
+        <v>162</v>
       </c>
       <c r="B185" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C185" t="s">
         <v>1</v>
-      </c>
-      <c r="D185" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>163</v>
+        <v>636</v>
       </c>
       <c r="B186" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C186" t="s">
         <v>1</v>
+      </c>
+      <c r="D186" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>458</v>
+        <v>163</v>
       </c>
       <c r="B187" t="s">
-        <v>459</v>
+        <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>582</v>
+        <v>458</v>
       </c>
       <c r="B188" t="s">
-        <v>583</v>
+        <v>459</v>
       </c>
       <c r="C188" t="s">
         <v>2</v>
@@ -5081,10 +5090,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>164</v>
+        <v>582</v>
       </c>
       <c r="B189" t="s">
-        <v>165</v>
+        <v>583</v>
       </c>
       <c r="C189" t="s">
         <v>2</v>
@@ -5092,10 +5101,10 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B190" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="C190" t="s">
         <v>2</v>
@@ -5103,57 +5112,57 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>460</v>
+        <v>166</v>
       </c>
       <c r="B191" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C191" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B192" t="s">
-        <v>462</v>
+        <v>11</v>
       </c>
       <c r="C192" t="s">
-        <v>2</v>
-      </c>
-      <c r="D192" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>167</v>
+        <v>461</v>
       </c>
       <c r="B193" t="s">
-        <v>551</v>
+        <v>462</v>
       </c>
       <c r="C193" t="s">
         <v>2</v>
+      </c>
+      <c r="D193" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B194" t="s">
-        <v>9</v>
+        <v>551</v>
       </c>
       <c r="C194" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B195" t="s">
-        <v>552</v>
+        <v>9</v>
       </c>
       <c r="C195" t="s">
         <v>1</v>
@@ -5161,10 +5170,10 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B196" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C196" t="s">
         <v>1</v>
@@ -5172,68 +5181,68 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B197" t="s">
-        <v>172</v>
+        <v>553</v>
       </c>
       <c r="C197" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B198" t="s">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="C198" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>554</v>
+        <v>173</v>
       </c>
       <c r="B199" t="s">
         <v>9</v>
       </c>
       <c r="C199" t="s">
         <v>1</v>
-      </c>
-      <c r="D199" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>174</v>
+        <v>554</v>
       </c>
       <c r="B200" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C200" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D200" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B201" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C201" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B202" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C202" t="s">
         <v>1</v>
@@ -5241,79 +5250,79 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>555</v>
+        <v>176</v>
       </c>
       <c r="B203" t="s">
-        <v>556</v>
+        <v>9</v>
       </c>
       <c r="C203" t="s">
         <v>1</v>
-      </c>
-      <c r="D203" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>463</v>
+        <v>555</v>
       </c>
       <c r="B204" t="s">
-        <v>479</v>
+        <v>556</v>
       </c>
       <c r="C204" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D204" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>177</v>
+        <v>463</v>
       </c>
       <c r="B205" t="s">
-        <v>558</v>
+        <v>479</v>
       </c>
       <c r="C205" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>559</v>
+        <v>177</v>
       </c>
       <c r="B206" t="s">
-        <v>9</v>
+        <v>558</v>
       </c>
       <c r="C206" t="s">
         <v>1</v>
-      </c>
-      <c r="D206" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>178</v>
+        <v>559</v>
       </c>
       <c r="B207" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C207" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D207" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B208" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C208" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B209" t="s">
         <v>13</v>
@@ -5324,7 +5333,7 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>424</v>
+        <v>180</v>
       </c>
       <c r="B210" t="s">
         <v>13</v>
@@ -5332,121 +5341,121 @@
       <c r="C210" t="s">
         <v>1</v>
       </c>
-      <c r="D210" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>181</v>
+        <v>424</v>
       </c>
       <c r="B211" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C211" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D211" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B212" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C212" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B213" t="s">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="C213" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>560</v>
+        <v>183</v>
       </c>
       <c r="B214" t="s">
-        <v>53</v>
+        <v>184</v>
       </c>
       <c r="C214" t="s">
-        <v>1</v>
-      </c>
-      <c r="D214" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>464</v>
+        <v>560</v>
       </c>
       <c r="B215" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C215" t="s">
         <v>1</v>
+      </c>
+      <c r="D215" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B216" t="s">
-        <v>466</v>
+        <v>9</v>
       </c>
       <c r="C216" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>644</v>
+        <v>465</v>
       </c>
       <c r="B217" t="s">
-        <v>361</v>
+        <v>466</v>
       </c>
       <c r="C217" t="s">
-        <v>1</v>
-      </c>
-      <c r="D217" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>185</v>
+        <v>644</v>
       </c>
       <c r="B218" t="s">
-        <v>13</v>
+        <v>361</v>
       </c>
       <c r="C218" t="s">
         <v>1</v>
+      </c>
+      <c r="D218" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B219" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>467</v>
+        <v>186</v>
       </c>
       <c r="B220" t="s">
-        <v>548</v>
+        <v>187</v>
       </c>
       <c r="C220" t="s">
         <v>2</v>
@@ -5454,10 +5463,10 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>188</v>
+        <v>467</v>
       </c>
       <c r="B221" t="s">
-        <v>38</v>
+        <v>548</v>
       </c>
       <c r="C221" t="s">
         <v>2</v>
@@ -5465,21 +5474,21 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B222" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C222" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B223" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C223" t="s">
         <v>1</v>
@@ -5487,21 +5496,18 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>561</v>
+        <v>190</v>
       </c>
       <c r="B224" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C224" t="s">
-        <v>2</v>
-      </c>
-      <c r="D224" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B225" t="s">
         <v>38</v>
@@ -5515,13 +5521,13 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B226" t="s">
-        <v>564</v>
+        <v>38</v>
       </c>
       <c r="C226" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D226" t="s">
         <v>415</v>
@@ -5529,21 +5535,24 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>191</v>
+        <v>563</v>
       </c>
       <c r="B227" t="s">
-        <v>20</v>
+        <v>564</v>
       </c>
       <c r="C227" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D227" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B228" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="C228" t="s">
         <v>2</v>
@@ -5551,21 +5560,21 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B229" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="C229" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B230" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C230" t="s">
         <v>1</v>
@@ -5573,24 +5582,21 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>423</v>
+        <v>194</v>
       </c>
       <c r="B231" t="s">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="C231" t="s">
-        <v>2</v>
-      </c>
-      <c r="D231" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>645</v>
+        <v>423</v>
       </c>
       <c r="B232" t="s">
-        <v>646</v>
+        <v>38</v>
       </c>
       <c r="C232" t="s">
         <v>2</v>
@@ -5601,32 +5607,35 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>195</v>
+        <v>645</v>
       </c>
       <c r="B233" t="s">
-        <v>63</v>
+        <v>646</v>
       </c>
       <c r="C233" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D233" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B234" t="s">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="C234" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B235" t="s">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="C235" t="s">
         <v>2</v>
@@ -5634,74 +5643,71 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B236" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C236" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B237" t="s">
-        <v>468</v>
+        <v>9</v>
       </c>
       <c r="C237" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>566</v>
+        <v>200</v>
       </c>
       <c r="B238" t="s">
-        <v>136</v>
+        <v>468</v>
       </c>
       <c r="C238" t="s">
-        <v>1</v>
-      </c>
-      <c r="D238" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>201</v>
+        <v>566</v>
       </c>
       <c r="B239" t="s">
-        <v>257</v>
+        <v>136</v>
       </c>
       <c r="C239" t="s">
         <v>1</v>
+      </c>
+      <c r="D239" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>567</v>
+        <v>201</v>
       </c>
       <c r="B240" t="s">
-        <v>568</v>
+        <v>257</v>
       </c>
       <c r="C240" t="s">
-        <v>2</v>
-      </c>
-      <c r="D240" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B241" t="s">
-        <v>9</v>
+        <v>568</v>
       </c>
       <c r="C241" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D241" t="s">
         <v>415</v>
@@ -5709,79 +5715,82 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>202</v>
+        <v>569</v>
       </c>
       <c r="B242" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="C242" t="s">
         <v>1</v>
+      </c>
+      <c r="D242" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B243" t="s">
-        <v>254</v>
+        <v>93</v>
       </c>
       <c r="C243" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>640</v>
+        <v>203</v>
       </c>
       <c r="B244" t="s">
-        <v>11</v>
+        <v>254</v>
       </c>
       <c r="C244" t="s">
-        <v>1</v>
-      </c>
-      <c r="D244" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>469</v>
+        <v>640</v>
       </c>
       <c r="B245" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C245" t="s">
         <v>1</v>
+      </c>
+      <c r="D245" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>204</v>
+        <v>469</v>
       </c>
       <c r="B246" t="s">
-        <v>570</v>
+        <v>13</v>
       </c>
       <c r="C246" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B247" t="s">
-        <v>9</v>
+        <v>570</v>
       </c>
       <c r="C247" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B248" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C248" t="s">
         <v>1</v>
@@ -5789,54 +5798,54 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B249" t="s">
-        <v>571</v>
+        <v>13</v>
       </c>
       <c r="C249" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B250" t="s">
-        <v>9</v>
+        <v>571</v>
       </c>
       <c r="C250" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B251" t="s">
-        <v>557</v>
+        <v>9</v>
       </c>
       <c r="C251" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B252" t="s">
-        <v>211</v>
+        <v>557</v>
       </c>
       <c r="C252" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B253" t="s">
-        <v>572</v>
+        <v>211</v>
       </c>
       <c r="C253" t="s">
         <v>1</v>
@@ -5844,57 +5853,54 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B254" t="s">
-        <v>214</v>
+        <v>572</v>
       </c>
       <c r="C254" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B255" t="s">
-        <v>573</v>
+        <v>214</v>
       </c>
       <c r="C255" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B256" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="C256" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>574</v>
+        <v>216</v>
       </c>
       <c r="B257" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C257" t="s">
         <v>2</v>
-      </c>
-      <c r="D257" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>217</v>
+        <v>574</v>
       </c>
       <c r="B258" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C258" t="s">
         <v>2</v>
@@ -5905,13 +5911,13 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B259" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C259" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D259" t="s">
         <v>415</v>
@@ -5919,21 +5925,24 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B260" t="s">
         <v>9</v>
       </c>
       <c r="C260" t="s">
         <v>1</v>
+      </c>
+      <c r="D260" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B261" t="s">
-        <v>221</v>
+        <v>9</v>
       </c>
       <c r="C261" t="s">
         <v>1</v>
@@ -5941,10 +5950,10 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B262" t="s">
-        <v>9</v>
+        <v>221</v>
       </c>
       <c r="C262" t="s">
         <v>1</v>
@@ -5952,7 +5961,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B263" t="s">
         <v>9</v>
@@ -5963,57 +5972,57 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>575</v>
+        <v>223</v>
       </c>
       <c r="B264" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C264" t="s">
-        <v>2</v>
-      </c>
-      <c r="D264" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="B265" t="s">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="C265" t="s">
         <v>2</v>
+      </c>
+      <c r="D265" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>224</v>
+        <v>470</v>
       </c>
       <c r="B266" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="C266" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B267" t="s">
-        <v>576</v>
+        <v>9</v>
       </c>
       <c r="C267" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B268" t="s">
-        <v>214</v>
+        <v>576</v>
       </c>
       <c r="C268" t="s">
         <v>2</v>
@@ -6021,35 +6030,35 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B269" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="C269" t="s">
-        <v>1</v>
-      </c>
-      <c r="D269" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>422</v>
+        <v>227</v>
       </c>
       <c r="B270" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C270" t="s">
         <v>1</v>
+      </c>
+      <c r="D270" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>228</v>
+        <v>422</v>
       </c>
       <c r="B271" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C271" t="s">
         <v>1</v>
@@ -6057,35 +6066,35 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>577</v>
+        <v>228</v>
       </c>
       <c r="B272" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C272" t="s">
         <v>1</v>
-      </c>
-      <c r="D272" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>229</v>
+        <v>577</v>
       </c>
       <c r="B273" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C273" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D273" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>471</v>
+        <v>229</v>
       </c>
       <c r="B274" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C274" t="s">
         <v>2</v>
@@ -6093,21 +6102,21 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>230</v>
+        <v>471</v>
       </c>
       <c r="B275" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C275" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B276" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C276" t="s">
         <v>1</v>
@@ -6115,57 +6124,57 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>578</v>
+        <v>231</v>
       </c>
       <c r="B277" t="s">
-        <v>579</v>
+        <v>11</v>
       </c>
       <c r="C277" t="s">
         <v>1</v>
-      </c>
-      <c r="D277" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>472</v>
+        <v>578</v>
       </c>
       <c r="B278" t="s">
-        <v>9</v>
+        <v>579</v>
       </c>
       <c r="C278" t="s">
         <v>1</v>
+      </c>
+      <c r="D278" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="B279" t="s">
-        <v>580</v>
+        <v>9</v>
       </c>
       <c r="C279" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B280" t="s">
-        <v>13</v>
+        <v>580</v>
       </c>
       <c r="C280" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B281" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C281" t="s">
         <v>1</v>
@@ -6173,10 +6182,10 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B282" t="s">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="C282" t="s">
         <v>1</v>
@@ -6184,24 +6193,21 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B283" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="C283" t="s">
         <v>1</v>
-      </c>
-      <c r="D283" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>584</v>
+        <v>236</v>
       </c>
       <c r="B284" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C284" t="s">
         <v>1</v>
@@ -6212,93 +6218,96 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>237</v>
+        <v>584</v>
       </c>
       <c r="B285" t="s">
-        <v>238</v>
+        <v>136</v>
       </c>
       <c r="C285" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D285" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>585</v>
+        <v>237</v>
       </c>
       <c r="B286" t="s">
-        <v>9</v>
+        <v>238</v>
       </c>
       <c r="C286" t="s">
-        <v>1</v>
-      </c>
-      <c r="D286" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>239</v>
+        <v>585</v>
       </c>
       <c r="B287" t="s">
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="C287" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D287" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>586</v>
+        <v>239</v>
       </c>
       <c r="B288" t="s">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="C288" t="s">
-        <v>1</v>
-      </c>
-      <c r="D288" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>241</v>
+        <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>242</v>
+        <v>55</v>
       </c>
       <c r="C289" t="s">
         <v>1</v>
+      </c>
+      <c r="D289" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B290" t="s">
-        <v>102</v>
+        <v>242</v>
       </c>
       <c r="C290" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B291" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="C291" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B292" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C292" t="s">
         <v>1</v>
@@ -6306,21 +6315,21 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B293" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="C293" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B294" t="s">
-        <v>197</v>
+        <v>113</v>
       </c>
       <c r="C294" t="s">
         <v>2</v>
@@ -6328,35 +6337,35 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>428</v>
+        <v>247</v>
       </c>
       <c r="B295" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="C295" t="s">
-        <v>1</v>
-      </c>
-      <c r="D295" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>248</v>
+        <v>428</v>
       </c>
       <c r="B296" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C296" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D296" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B297" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
       <c r="C297" t="s">
         <v>2</v>
@@ -6364,10 +6373,10 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B298" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C298" t="s">
         <v>2</v>
@@ -6375,10 +6384,10 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B299" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C299" t="s">
         <v>2</v>
@@ -6386,21 +6395,18 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>587</v>
+        <v>253</v>
       </c>
       <c r="B300" t="s">
-        <v>9</v>
+        <v>254</v>
       </c>
       <c r="C300" t="s">
-        <v>1</v>
-      </c>
-      <c r="D300" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>425</v>
+        <v>587</v>
       </c>
       <c r="B301" t="s">
         <v>9</v>
@@ -6414,18 +6420,21 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>255</v>
+        <v>425</v>
       </c>
       <c r="B302" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C302" t="s">
         <v>1</v>
+      </c>
+      <c r="D302" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B303" t="s">
         <v>13</v>
@@ -6436,71 +6445,71 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>588</v>
+        <v>256</v>
       </c>
       <c r="B304" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C304" t="s">
-        <v>2</v>
-      </c>
-      <c r="D304" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>258</v>
+        <v>588</v>
       </c>
       <c r="B305" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C305" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D305" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B306" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C306" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>589</v>
+        <v>259</v>
       </c>
       <c r="B307" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C307" t="s">
-        <v>1</v>
-      </c>
-      <c r="D307" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>260</v>
+        <v>589</v>
       </c>
       <c r="B308" t="s">
         <v>9</v>
       </c>
       <c r="C308" t="s">
         <v>1</v>
+      </c>
+      <c r="D308" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B309" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C309" t="s">
         <v>1</v>
@@ -6508,10 +6517,10 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B310" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C310" t="s">
         <v>1</v>
@@ -6519,10 +6528,10 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B311" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C311" t="s">
         <v>1</v>
@@ -6530,29 +6539,29 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B312" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
       <c r="C312" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B313" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="C313" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B314" t="s">
         <v>9</v>
@@ -6563,21 +6572,21 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B315" t="s">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="C315" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B316" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C316" t="s">
         <v>2</v>
@@ -6585,46 +6594,46 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B317" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C317" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>590</v>
+        <v>271</v>
       </c>
       <c r="B318" t="s">
-        <v>55</v>
+        <v>272</v>
       </c>
       <c r="C318" t="s">
         <v>1</v>
-      </c>
-      <c r="D318" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>274</v>
+        <v>590</v>
       </c>
       <c r="B319" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C319" t="s">
         <v>1</v>
+      </c>
+      <c r="D319" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B320" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C320" t="s">
         <v>1</v>
@@ -6632,79 +6641,79 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>473</v>
+        <v>275</v>
       </c>
       <c r="B321" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="C321" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>276</v>
+        <v>473</v>
       </c>
       <c r="B322" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C322" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>591</v>
+        <v>276</v>
       </c>
       <c r="B323" t="s">
-        <v>592</v>
+        <v>55</v>
       </c>
       <c r="C323" t="s">
-        <v>2</v>
-      </c>
-      <c r="D323" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>277</v>
+        <v>591</v>
       </c>
       <c r="B324" t="s">
-        <v>9</v>
+        <v>592</v>
       </c>
       <c r="C324" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D324" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>593</v>
+        <v>277</v>
       </c>
       <c r="B325" t="s">
-        <v>594</v>
+        <v>9</v>
       </c>
       <c r="C325" t="s">
-        <v>2</v>
-      </c>
-      <c r="D325" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>278</v>
+        <v>593</v>
       </c>
       <c r="B326" t="s">
-        <v>9</v>
+        <v>594</v>
       </c>
       <c r="C326" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D326" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B327" t="s">
         <v>9</v>
@@ -6715,10 +6724,10 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B328" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C328" t="s">
         <v>1</v>
@@ -6726,10 +6735,10 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B329" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C329" t="s">
         <v>1</v>
@@ -6737,7 +6746,7 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B330" t="s">
         <v>9</v>
@@ -6748,21 +6757,21 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>474</v>
+        <v>282</v>
       </c>
       <c r="B331" t="s">
-        <v>452</v>
+        <v>9</v>
       </c>
       <c r="C331" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B332" t="s">
-        <v>20</v>
+        <v>452</v>
       </c>
       <c r="C332" t="s">
         <v>2</v>
@@ -6770,10 +6779,10 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>283</v>
+        <v>475</v>
       </c>
       <c r="B333" t="s">
-        <v>273</v>
+        <v>20</v>
       </c>
       <c r="C333" t="s">
         <v>2</v>
@@ -6781,18 +6790,18 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B334" t="s">
-        <v>9</v>
+        <v>273</v>
       </c>
       <c r="C334" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B335" t="s">
         <v>9</v>
@@ -6803,60 +6812,57 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B336" t="s">
-        <v>287</v>
+        <v>9</v>
       </c>
       <c r="C336" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>595</v>
+        <v>286</v>
       </c>
       <c r="B337" t="s">
-        <v>596</v>
+        <v>287</v>
       </c>
       <c r="C337" t="s">
-        <v>1</v>
-      </c>
-      <c r="D337" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>476</v>
+        <v>595</v>
       </c>
       <c r="B338" t="s">
-        <v>13</v>
+        <v>596</v>
       </c>
       <c r="C338" t="s">
         <v>1</v>
+      </c>
+      <c r="D338" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>641</v>
+        <v>476</v>
       </c>
       <c r="B339" t="s">
-        <v>580</v>
+        <v>13</v>
       </c>
       <c r="C339" t="s">
-        <v>2</v>
-      </c>
-      <c r="D339" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="B340" t="s">
-        <v>293</v>
+        <v>580</v>
       </c>
       <c r="C340" t="s">
         <v>2</v>
@@ -6867,65 +6873,68 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>288</v>
+        <v>597</v>
       </c>
       <c r="B341" t="s">
-        <v>68</v>
+        <v>293</v>
       </c>
       <c r="C341" t="s">
         <v>2</v>
+      </c>
+      <c r="D341" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B342" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C342" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B343" t="s">
-        <v>466</v>
+        <v>13</v>
       </c>
       <c r="C343" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B344" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C344" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B345" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C345" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B346" t="s">
-        <v>477</v>
+        <v>20</v>
       </c>
       <c r="C346" t="s">
         <v>2</v>
@@ -6933,21 +6942,21 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B347" t="s">
-        <v>55</v>
+        <v>477</v>
       </c>
       <c r="C347" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B348" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="C348" t="s">
         <v>1</v>
@@ -6955,10 +6964,10 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B349" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="C349" t="s">
         <v>1</v>
@@ -6966,68 +6975,68 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B350" t="s">
-        <v>240</v>
+        <v>13</v>
       </c>
       <c r="C350" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B351" t="s">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="C351" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>497</v>
+        <v>299</v>
       </c>
       <c r="B352" t="s">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="C352" t="s">
         <v>1</v>
-      </c>
-      <c r="D352" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>300</v>
+        <v>497</v>
       </c>
       <c r="B353" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C353" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D353" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B354" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C354" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>478</v>
+        <v>301</v>
       </c>
       <c r="B355" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C355" t="s">
         <v>1</v>
@@ -7035,68 +7044,65 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>302</v>
+        <v>478</v>
       </c>
       <c r="B356" t="s">
-        <v>293</v>
+        <v>13</v>
       </c>
       <c r="C356" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B357" t="s">
-        <v>9</v>
+        <v>293</v>
       </c>
       <c r="C357" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B358" t="s">
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="C358" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B359" t="s">
-        <v>9</v>
+        <v>240</v>
       </c>
       <c r="C359" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>598</v>
+        <v>305</v>
       </c>
       <c r="B360" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C360" t="s">
         <v>1</v>
-      </c>
-      <c r="D360" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B361" t="s">
-        <v>600</v>
+        <v>13</v>
       </c>
       <c r="C361" t="s">
         <v>1</v>
@@ -7107,13 +7113,13 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B362" t="s">
-        <v>4</v>
+        <v>600</v>
       </c>
       <c r="C362" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D362" t="s">
         <v>415</v>
@@ -7121,21 +7127,24 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>306</v>
+        <v>601</v>
       </c>
       <c r="B363" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C363" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D363" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B364" t="s">
-        <v>308</v>
+        <v>13</v>
       </c>
       <c r="C364" t="s">
         <v>1</v>
@@ -7143,32 +7152,32 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B365" t="s">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="C365" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B366" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C366" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B367" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C367" t="s">
         <v>1</v>
@@ -7176,10 +7185,10 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B368" t="s">
-        <v>314</v>
+        <v>13</v>
       </c>
       <c r="C368" t="s">
         <v>1</v>
@@ -7187,35 +7196,35 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>602</v>
+        <v>313</v>
       </c>
       <c r="B369" t="s">
-        <v>603</v>
+        <v>314</v>
       </c>
       <c r="C369" t="s">
         <v>1</v>
-      </c>
-      <c r="D369" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>315</v>
+        <v>602</v>
       </c>
       <c r="B370" t="s">
-        <v>9</v>
+        <v>603</v>
       </c>
       <c r="C370" t="s">
         <v>1</v>
+      </c>
+      <c r="D370" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B371" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="C371" t="s">
         <v>1</v>
@@ -7223,32 +7232,32 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B372" t="s">
-        <v>318</v>
+        <v>91</v>
       </c>
       <c r="C372" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B373" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C373" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B374" t="s">
-        <v>91</v>
+        <v>320</v>
       </c>
       <c r="C374" t="s">
         <v>1</v>
@@ -7256,10 +7265,10 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B375" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="C375" t="s">
         <v>1</v>
@@ -7267,35 +7276,35 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>604</v>
+        <v>322</v>
       </c>
       <c r="B376" t="s">
-        <v>605</v>
+        <v>9</v>
       </c>
       <c r="C376" t="s">
-        <v>2</v>
-      </c>
-      <c r="D376" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>323</v>
+        <v>604</v>
       </c>
       <c r="B377" t="s">
-        <v>13</v>
+        <v>605</v>
       </c>
       <c r="C377" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D377" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B378" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C378" t="s">
         <v>1</v>
@@ -7303,46 +7312,46 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>606</v>
+        <v>324</v>
       </c>
       <c r="B379" t="s">
-        <v>580</v>
+        <v>9</v>
       </c>
       <c r="C379" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B380" t="s">
-        <v>20</v>
+        <v>580</v>
       </c>
       <c r="C380" t="s">
         <v>2</v>
-      </c>
-      <c r="D380" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>325</v>
+        <v>607</v>
       </c>
       <c r="B381" t="s">
-        <v>608</v>
+        <v>20</v>
       </c>
       <c r="C381" t="s">
         <v>2</v>
+      </c>
+      <c r="D381" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B382" t="s">
-        <v>20</v>
+        <v>608</v>
       </c>
       <c r="C382" t="s">
         <v>2</v>
@@ -7350,21 +7359,21 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B383" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C383" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B384" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C384" t="s">
         <v>1</v>
@@ -7372,35 +7381,35 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>647</v>
+        <v>329</v>
       </c>
       <c r="B385" t="s">
-        <v>466</v>
+        <v>0</v>
       </c>
       <c r="C385" t="s">
-        <v>2</v>
-      </c>
-      <c r="D385" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>330</v>
+        <v>647</v>
       </c>
       <c r="B386" t="s">
-        <v>609</v>
+        <v>466</v>
       </c>
       <c r="C386" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D386" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B387" t="s">
-        <v>6</v>
+        <v>609</v>
       </c>
       <c r="C387" t="s">
         <v>1</v>
@@ -7408,10 +7417,10 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B388" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C388" t="s">
         <v>1</v>
@@ -7419,10 +7428,10 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B389" t="s">
-        <v>326</v>
+        <v>13</v>
       </c>
       <c r="C389" t="s">
         <v>1</v>
@@ -7430,35 +7439,35 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>610</v>
+        <v>333</v>
       </c>
       <c r="B390" t="s">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="C390" t="s">
-        <v>2</v>
-      </c>
-      <c r="D390" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>334</v>
+        <v>610</v>
       </c>
       <c r="B391" t="s">
-        <v>361</v>
+        <v>20</v>
       </c>
       <c r="C391" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D391" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B392" t="s">
-        <v>9</v>
+        <v>361</v>
       </c>
       <c r="C392" t="s">
         <v>1</v>
@@ -7466,71 +7475,71 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B393" t="s">
         <v>9</v>
       </c>
       <c r="C393" t="s">
         <v>1</v>
-      </c>
-      <c r="D393" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B394" t="s">
         <v>9</v>
       </c>
       <c r="C394" t="s">
         <v>1</v>
+      </c>
+      <c r="D394" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B395" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="C395" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B396" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C396" t="s">
-        <v>1</v>
-      </c>
-      <c r="D396" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B397" t="s">
         <v>9</v>
       </c>
       <c r="C397" t="s">
         <v>1</v>
+      </c>
+      <c r="D397" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B398" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C398" t="s">
         <v>1</v>
@@ -7538,7 +7547,7 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>426</v>
+        <v>341</v>
       </c>
       <c r="B399" t="s">
         <v>13</v>
@@ -7546,19 +7555,16 @@
       <c r="C399" t="s">
         <v>1</v>
       </c>
-      <c r="D399" t="s">
-        <v>415</v>
-      </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B400" t="s">
-        <v>611</v>
+        <v>13</v>
       </c>
       <c r="C400" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D400" t="s">
         <v>415</v>
@@ -7566,21 +7572,24 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>342</v>
+        <v>420</v>
       </c>
       <c r="B401" t="s">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="C401" t="s">
         <v>2</v>
+      </c>
+      <c r="D401" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B402" t="s">
-        <v>197</v>
+        <v>580</v>
       </c>
       <c r="C402" t="s">
         <v>2</v>
@@ -7588,21 +7597,21 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B403" t="s">
-        <v>9</v>
+        <v>197</v>
       </c>
       <c r="C403" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B404" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C404" t="s">
         <v>1</v>
@@ -7610,10 +7619,10 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B405" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C405" t="s">
         <v>1</v>
@@ -7621,21 +7630,18 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>480</v>
+        <v>346</v>
       </c>
       <c r="B406" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C406" t="s">
-        <v>2</v>
-      </c>
-      <c r="D406" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>612</v>
+        <v>480</v>
       </c>
       <c r="B407" t="s">
         <v>38</v>
@@ -7649,21 +7655,24 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>347</v>
+        <v>612</v>
       </c>
       <c r="B408" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C408" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D408" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B409" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C409" t="s">
         <v>1</v>
@@ -7671,7 +7680,7 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B410" t="s">
         <v>13</v>
@@ -7682,52 +7691,49 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>613</v>
+        <v>349</v>
       </c>
       <c r="B411" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C411" t="s">
-        <v>2</v>
-      </c>
-      <c r="D411" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>350</v>
+        <v>613</v>
       </c>
       <c r="B412" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C412" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D412" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>614</v>
+        <v>350</v>
       </c>
       <c r="B413" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C413" t="s">
         <v>1</v>
-      </c>
-      <c r="D413" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>493</v>
+        <v>614</v>
       </c>
       <c r="B414" t="s">
-        <v>452</v>
+        <v>13</v>
       </c>
       <c r="C414" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D414" t="s">
         <v>415</v>
@@ -7735,49 +7741,49 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>351</v>
+        <v>493</v>
       </c>
       <c r="B415" t="s">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="C415" t="s">
         <v>2</v>
+      </c>
+      <c r="D415" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B416" t="s">
-        <v>311</v>
+        <v>481</v>
       </c>
       <c r="C416" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>482</v>
+        <v>352</v>
       </c>
       <c r="B417" t="s">
-        <v>38</v>
+        <v>311</v>
       </c>
       <c r="C417" t="s">
-        <v>2</v>
-      </c>
-      <c r="D417" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>615</v>
+        <v>482</v>
       </c>
       <c r="B418" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C418" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D418" t="s">
         <v>415</v>
@@ -7785,38 +7791,38 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>353</v>
+        <v>615</v>
       </c>
       <c r="B419" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C419" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D419" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>616</v>
+        <v>353</v>
       </c>
       <c r="B420" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C420" t="s">
-        <v>1</v>
-      </c>
-      <c r="D420" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>483</v>
+        <v>616</v>
       </c>
       <c r="B421" t="s">
-        <v>617</v>
+        <v>9</v>
       </c>
       <c r="C421" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D421" t="s">
         <v>415</v>
@@ -7824,49 +7830,49 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>354</v>
+        <v>483</v>
       </c>
       <c r="B422" t="s">
-        <v>13</v>
+        <v>617</v>
       </c>
       <c r="C422" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D422" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>484</v>
+        <v>354</v>
       </c>
       <c r="B423" t="s">
-        <v>355</v>
+        <v>13</v>
       </c>
       <c r="C423" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>356</v>
+        <v>484</v>
       </c>
       <c r="B424" t="s">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="C424" t="s">
         <v>2</v>
-      </c>
-      <c r="D424" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>618</v>
+        <v>356</v>
       </c>
       <c r="B425" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C425" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D425" t="s">
         <v>415</v>
@@ -7874,13 +7880,13 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B426" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C426" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D426" t="s">
         <v>415</v>
@@ -7888,32 +7894,35 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>357</v>
+        <v>619</v>
       </c>
       <c r="B427" t="s">
-        <v>481</v>
+        <v>20</v>
       </c>
       <c r="C427" t="s">
         <v>2</v>
+      </c>
+      <c r="D427" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B428" t="s">
-        <v>13</v>
+        <v>481</v>
       </c>
       <c r="C428" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B429" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C429" t="s">
         <v>1</v>
@@ -7921,10 +7930,10 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B430" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C430" t="s">
         <v>1</v>
@@ -7932,32 +7941,32 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B431" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C431" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B432" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C432" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B433" t="s">
-        <v>365</v>
+        <v>13</v>
       </c>
       <c r="C433" t="s">
         <v>1</v>
@@ -7965,35 +7974,35 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>620</v>
+        <v>364</v>
       </c>
       <c r="B434" t="s">
-        <v>38</v>
+        <v>365</v>
       </c>
       <c r="C434" t="s">
         <v>1</v>
-      </c>
-      <c r="D434" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>366</v>
+        <v>620</v>
       </c>
       <c r="B435" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="C435" t="s">
         <v>1</v>
+      </c>
+      <c r="D435" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B436" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C436" t="s">
         <v>1</v>
@@ -8001,32 +8010,32 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>485</v>
+        <v>367</v>
       </c>
       <c r="B437" t="s">
-        <v>486</v>
+        <v>9</v>
       </c>
       <c r="C437" t="s">
-        <v>2</v>
-      </c>
-      <c r="D437" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>368</v>
+        <v>485</v>
       </c>
       <c r="B438" t="s">
-        <v>9</v>
+        <v>486</v>
       </c>
       <c r="C438" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D438" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B439" t="s">
         <v>9</v>
@@ -8037,10 +8046,10 @@
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B440" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C440" t="s">
         <v>1</v>
@@ -8048,35 +8057,35 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>648</v>
+        <v>370</v>
       </c>
       <c r="B441" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C441" t="s">
-        <v>2</v>
-      </c>
-      <c r="D441" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>371</v>
+        <v>648</v>
       </c>
       <c r="B442" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C442" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D442" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B443" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C443" t="s">
         <v>1</v>
@@ -8084,27 +8093,24 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>621</v>
+        <v>372</v>
       </c>
       <c r="B444" t="s">
-        <v>622</v>
+        <v>13</v>
       </c>
       <c r="C444" t="s">
         <v>1</v>
-      </c>
-      <c r="D444" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B445" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C445" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D445" t="s">
         <v>415</v>
@@ -8112,101 +8118,104 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>373</v>
+        <v>623</v>
       </c>
       <c r="B446" t="s">
-        <v>55</v>
+        <v>624</v>
       </c>
       <c r="C446" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D446" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B447" t="s">
-        <v>375</v>
+        <v>55</v>
       </c>
       <c r="C447" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B448" t="s">
-        <v>13</v>
+        <v>375</v>
       </c>
       <c r="C448" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B449" t="s">
-        <v>625</v>
+        <v>13</v>
       </c>
       <c r="C449" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B450" t="s">
-        <v>9</v>
+        <v>625</v>
       </c>
       <c r="C450" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>487</v>
+        <v>378</v>
       </c>
       <c r="B451" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C451" t="s">
         <v>1</v>
-      </c>
-      <c r="D451" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="B452" t="s">
-        <v>380</v>
+        <v>11</v>
       </c>
       <c r="C452" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D452" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B453" t="s">
-        <v>9</v>
+        <v>380</v>
       </c>
       <c r="C453" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B454" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C454" t="s">
         <v>1</v>
@@ -8214,60 +8223,60 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>626</v>
+        <v>382</v>
       </c>
       <c r="B455" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C455" t="s">
-        <v>2</v>
-      </c>
-      <c r="D455" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>383</v>
+        <v>626</v>
       </c>
       <c r="B456" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C456" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D456" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>627</v>
+        <v>383</v>
       </c>
       <c r="B457" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C457" t="s">
-        <v>2</v>
-      </c>
-      <c r="D457" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>384</v>
+        <v>627</v>
       </c>
       <c r="B458" t="s">
-        <v>486</v>
+        <v>20</v>
       </c>
       <c r="C458" t="s">
         <v>2</v>
+      </c>
+      <c r="D458" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="B459" t="s">
-        <v>20</v>
+        <v>486</v>
       </c>
       <c r="C459" t="s">
         <v>2</v>
@@ -8275,35 +8284,35 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>628</v>
+        <v>416</v>
       </c>
       <c r="B460" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C460" t="s">
-        <v>1</v>
-      </c>
-      <c r="D460" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>385</v>
+        <v>628</v>
       </c>
       <c r="B461" t="s">
-        <v>488</v>
+        <v>9</v>
       </c>
       <c r="C461" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D461" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B462" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C462" t="s">
         <v>2</v>
@@ -8311,35 +8320,35 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>629</v>
+        <v>386</v>
       </c>
       <c r="B463" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="C463" t="s">
-        <v>1</v>
-      </c>
-      <c r="D463" t="s">
-        <v>415</v>
+        <v>2</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B464" t="s">
-        <v>631</v>
+        <v>9</v>
       </c>
       <c r="C464" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D464" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>387</v>
+        <v>630</v>
       </c>
       <c r="B465" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C465" t="s">
         <v>2</v>
@@ -8347,21 +8356,21 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B466" t="s">
-        <v>326</v>
+        <v>632</v>
       </c>
       <c r="C466" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B467" t="s">
-        <v>9</v>
+        <v>326</v>
       </c>
       <c r="C467" t="s">
         <v>1</v>
@@ -8369,32 +8378,32 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B468" t="s">
-        <v>490</v>
+        <v>9</v>
       </c>
       <c r="C468" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B469" t="s">
-        <v>9</v>
+        <v>490</v>
       </c>
       <c r="C469" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B470" t="s">
-        <v>136</v>
+        <v>9</v>
       </c>
       <c r="C470" t="s">
         <v>1</v>
@@ -8402,10 +8411,10 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>633</v>
+        <v>392</v>
       </c>
       <c r="B471" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="C471" t="s">
         <v>1</v>
@@ -8413,10 +8422,10 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>393</v>
+        <v>633</v>
       </c>
       <c r="B472" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C472" t="s">
         <v>1</v>
@@ -8424,7 +8433,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B473" t="s">
         <v>13</v>
@@ -8435,10 +8444,10 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B474" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="C474" t="s">
         <v>1</v>
@@ -8446,10 +8455,10 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B475" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="C475" t="s">
         <v>1</v>
@@ -8457,7 +8466,7 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B476" t="s">
         <v>9</v>
@@ -8468,60 +8477,60 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>634</v>
+        <v>397</v>
       </c>
       <c r="B477" t="s">
         <v>9</v>
       </c>
       <c r="C477" t="s">
         <v>1</v>
-      </c>
-      <c r="D477" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>398</v>
+        <v>634</v>
       </c>
       <c r="B478" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="C478" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D478" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>635</v>
+        <v>398</v>
       </c>
       <c r="B479" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="C479" t="s">
         <v>2</v>
-      </c>
-      <c r="D479" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>399</v>
+        <v>635</v>
       </c>
       <c r="B480" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C480" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D480" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B481" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C481" t="s">
         <v>1</v>
@@ -8529,10 +8538,10 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B482" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C482" t="s">
         <v>1</v>
@@ -8540,7 +8549,7 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B483" t="s">
         <v>9</v>
@@ -8551,35 +8560,35 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>637</v>
+        <v>402</v>
       </c>
       <c r="B484" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C484" t="s">
-        <v>2</v>
-      </c>
-      <c r="D484" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>403</v>
+        <v>637</v>
       </c>
       <c r="B485" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C485" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D485" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B486" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C486" t="s">
         <v>1</v>
@@ -8587,77 +8596,88 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B487" t="s">
-        <v>406</v>
+        <v>13</v>
       </c>
       <c r="C487" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B488" t="s">
-        <v>9</v>
+        <v>406</v>
       </c>
       <c r="C488" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>638</v>
+        <v>407</v>
       </c>
       <c r="B489" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C489" t="s">
-        <v>2</v>
-      </c>
-      <c r="D489" t="s">
-        <v>415</v>
+        <v>1</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>408</v>
+        <v>638</v>
       </c>
       <c r="B490" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C490" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D490" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>491</v>
+        <v>408</v>
       </c>
       <c r="B491" t="s">
-        <v>492</v>
+        <v>9</v>
       </c>
       <c r="C491" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
+        <v>491</v>
+      </c>
+      <c r="B492" t="s">
+        <v>492</v>
+      </c>
+      <c r="C492" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
         <v>409</v>
       </c>
-      <c r="B492" t="s">
+      <c r="B493" t="s">
         <v>13</v>
       </c>
-      <c r="C492" t="s">
+      <c r="C493" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{8F56ED3D-A3F2-450D-9EAE-1214C3EA2069}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D492">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="A1:D492" xr:uid="{8F56ED3D-A3F2-450D-9EAE-1214C3EA2069}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D493">
+      <sortCondition ref="A1:A492"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
